--- a/synthetic/src/test/resources/template.xlsx
+++ b/synthetic/src/test/resources/template.xlsx
@@ -865,47 +865,47 @@
         <f>IF($B6=725,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AL6" t="str" s="0">
+      <c r="AL6" t="str">
         <f>IF($B6=735,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AM6" t="str" s="0">
+      <c r="AM6" t="str">
         <f>IF($B6=727,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AN6" t="str" s="0">
+      <c r="AN6" t="str">
         <f>IF($B6=718,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AO6" t="str" s="0">
+      <c r="AO6" t="str">
         <f>IF($B6=719,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AP6" t="str" s="0">
+      <c r="AP6" t="str">
         <f>IF($B6=717,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AQ6" t="str" s="0">
+      <c r="AQ6" t="str">
         <f>IF($B6=722,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AR6" t="str" s="0">
+      <c r="AR6" t="str">
         <f>IF($B6=708,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AS6" t="str" s="0">
+      <c r="AS6" t="str">
         <f>IF($B6=701,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AT6" t="str" s="0">
+      <c r="AT6" t="str">
         <f>IF($B6=702,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AU6" t="str" s="0">
+      <c r="AU6" t="str">
         <f>IF($B6=731,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
-      <c r="AV6" t="str" s="0">
+      <c r="AV6" t="str">
         <f>IF($B6=730,SUM($G6-(SUM($H6:$I6))),"")</f>
         <v/>
       </c>
@@ -1044,18 +1044,6 @@
         <f>IF($B7=737,SUM($G7-(SUM($H7:$I7))),"")</f>
         <v/>
       </c>
-      <c r="AK7" t="str">
-        <f>IF($B7=725,SUM($G7-(SUM($H7:$I7))),"")</f>
-        <v/>
-      </c>
-      <c r="AL7" t="str">
-        <f>IF($B7=735,SUM($G7-(SUM($H7:$I7))),"")</f>
-        <v/>
-      </c>
-      <c r="AM7" t="str">
-        <f>IF($B7=727,SUM($G7-(SUM($H7:$I7))),"")</f>
-        <v/>
-      </c>
       <c r="AN7" t="str">
         <f>IF($B7=718,SUM($G7-(SUM($H7:$I7))),"")</f>
         <v/>
@@ -1089,7 +1077,7 @@
         <v/>
       </c>
       <c r="AV7" t="str">
-        <f>IF($B7=730,SUM($G7-(SUM($H7:$I7))),"")</f>
+        <f>IF($B7=735,SUM($G7-(SUM($H7:$I7))),"")</f>
         <v/>
       </c>
     </row>
@@ -1227,18 +1215,6 @@
         <f>IF($B8=737,SUM($G8-(SUM($H8:$I8))),"")</f>
         <v/>
       </c>
-      <c r="AK8" t="n">
-        <f>IF($B8=725,SUM($G8-(SUM($H8:$I8))),"")</f>
-        <v>0.0</v>
-      </c>
-      <c r="AL8" t="str">
-        <f>IF($B8=735,SUM($G8-(SUM($H8:$I8))),"")</f>
-        <v/>
-      </c>
-      <c r="AM8" t="str">
-        <f>IF($B8=727,SUM($G8-(SUM($H8:$I8))),"")</f>
-        <v/>
-      </c>
       <c r="AN8" t="str">
         <f>IF($B8=718,SUM($G8-(SUM($H8:$I8))),"")</f>
         <v/>
@@ -1272,7 +1248,7 @@
         <v/>
       </c>
       <c r="AV8" t="str">
-        <f>IF($B8=730,SUM($G8-(SUM($H8:$I8))),"")</f>
+        <f>IF($B8=735,SUM($G8-(SUM($H8:$I8))),"")</f>
         <v/>
       </c>
     </row>
@@ -1411,18 +1387,6 @@
         <f>IF($B9=737,SUM($G9-(SUM($H9:$I9))),"")</f>
         <v/>
       </c>
-      <c r="AK9" t="str">
-        <f>IF($B9=725,SUM($G9-(SUM($H9:$I9))),"")</f>
-        <v/>
-      </c>
-      <c r="AL9" t="str">
-        <f>IF($B9=735,SUM($G9-(SUM($H9:$I9))),"")</f>
-        <v/>
-      </c>
-      <c r="AM9" t="str">
-        <f>IF($B9=727,SUM($G9-(SUM($H9:$I9))),"")</f>
-        <v/>
-      </c>
       <c r="AN9" t="str">
         <f>IF($B9=718,SUM($G9-(SUM($H9:$I9))),"")</f>
         <v/>
@@ -1456,7 +1420,7 @@
         <v/>
       </c>
       <c r="AV9" t="str">
-        <f>IF($B9=730,SUM($G9-(SUM($H9:$I9))),"")</f>
+        <f>IF($B9=735,SUM($G9-(SUM($H9:$I9))),"")</f>
         <v/>
       </c>
     </row>
@@ -1594,18 +1558,6 @@
         <f>IF($B10=737,SUM($G10-(SUM($H10:$I10))),"")</f>
         <v/>
       </c>
-      <c r="AK10" t="str">
-        <f>IF($B10=725,SUM($G10-(SUM($H10:$I10))),"")</f>
-        <v/>
-      </c>
-      <c r="AL10" t="str">
-        <f>IF($B10=735,SUM($G10-(SUM($H10:$I10))),"")</f>
-        <v/>
-      </c>
-      <c r="AM10" t="n">
-        <f>IF($B10=727,SUM($G10-(SUM($H10:$I10))),"")</f>
-        <v>0.0</v>
-      </c>
       <c r="AN10" t="str">
         <f>IF($B10=718,SUM($G10-(SUM($H10:$I10))),"")</f>
         <v/>
@@ -1639,7 +1591,7 @@
         <v/>
       </c>
       <c r="AV10" t="str">
-        <f>IF($B10=730,SUM($G10-(SUM($H10:$I10))),"")</f>
+        <f>IF($B10=735,SUM($G10-(SUM($H10:$I10))),"")</f>
         <v/>
       </c>
     </row>
@@ -1777,18 +1729,6 @@
         <f>IF($B11=737,SUM($G11-(SUM($H11:$I11))),"")</f>
         <v/>
       </c>
-      <c r="AK11" t="str">
-        <f>IF($B11=725,SUM($G11-(SUM($H11:$I11))),"")</f>
-        <v/>
-      </c>
-      <c r="AL11" t="str">
-        <f>IF($B11=735,SUM($G11-(SUM($H11:$I11))),"")</f>
-        <v/>
-      </c>
-      <c r="AM11" t="str">
-        <f>IF($B11=727,SUM($G11-(SUM($H11:$I11))),"")</f>
-        <v/>
-      </c>
       <c r="AN11" t="str">
         <f>IF($B11=718,SUM($G11-(SUM($H11:$I11))),"")</f>
         <v/>
@@ -1822,7 +1762,7 @@
         <v/>
       </c>
       <c r="AV11" t="str">
-        <f>IF($B11=730,SUM($G11-(SUM($H11:$I11))),"")</f>
+        <f>IF($B11=735,SUM($G11-(SUM($H11:$I11))),"")</f>
         <v/>
       </c>
     </row>
@@ -1960,18 +1900,6 @@
         <f>IF($B12=737,SUM($G12-(SUM($H12:$I12))),"")</f>
         <v/>
       </c>
-      <c r="AK12" t="str">
-        <f>IF($B12=725,SUM($G12-(SUM($H12:$I12))),"")</f>
-        <v/>
-      </c>
-      <c r="AL12" t="str">
-        <f>IF($B12=735,SUM($G12-(SUM($H12:$I12))),"")</f>
-        <v/>
-      </c>
-      <c r="AM12" t="str">
-        <f>IF($B12=727,SUM($G12-(SUM($H12:$I12))),"")</f>
-        <v/>
-      </c>
       <c r="AN12" t="str">
         <f>IF($B12=718,SUM($G12-(SUM($H12:$I12))),"")</f>
         <v/>
@@ -2005,7 +1933,7 @@
         <v/>
       </c>
       <c r="AV12" t="str">
-        <f>IF($B12=730,SUM($G12-(SUM($H12:$I12))),"")</f>
+        <f>IF($B12=735,SUM($G12-(SUM($H12:$I12))),"")</f>
         <v/>
       </c>
     </row>
@@ -2143,18 +2071,6 @@
         <f>IF($B13=737,SUM($G13-(SUM($H13:$I13))),"")</f>
         <v/>
       </c>
-      <c r="AK13" t="str">
-        <f>IF($B13=725,SUM($G13-(SUM($H13:$I13))),"")</f>
-        <v/>
-      </c>
-      <c r="AL13" t="str">
-        <f>IF($B13=735,SUM($G13-(SUM($H13:$I13))),"")</f>
-        <v/>
-      </c>
-      <c r="AM13" t="str">
-        <f>IF($B13=727,SUM($G13-(SUM($H13:$I13))),"")</f>
-        <v/>
-      </c>
       <c r="AN13" t="str">
         <f>IF($B13=718,SUM($G13-(SUM($H13:$I13))),"")</f>
         <v/>
@@ -2188,7 +2104,7 @@
         <v/>
       </c>
       <c r="AV13" t="str">
-        <f>IF($B13=730,SUM($G13-(SUM($H13:$I13))),"")</f>
+        <f>IF($B13=735,SUM($G13-(SUM($H13:$I13))),"")</f>
         <v/>
       </c>
     </row>
@@ -2326,18 +2242,6 @@
         <f>IF($B14=737,SUM($G14-(SUM($H14:$I14))),"")</f>
         <v/>
       </c>
-      <c r="AK14" t="str">
-        <f>IF($B14=725,SUM($G14-(SUM($H14:$I14))),"")</f>
-        <v/>
-      </c>
-      <c r="AL14" t="str">
-        <f>IF($B14=735,SUM($G14-(SUM($H14:$I14))),"")</f>
-        <v/>
-      </c>
-      <c r="AM14" t="str">
-        <f>IF($B14=727,SUM($G14-(SUM($H14:$I14))),"")</f>
-        <v/>
-      </c>
       <c r="AN14" t="str">
         <f>IF($B14=718,SUM($G14-(SUM($H14:$I14))),"")</f>
         <v/>
@@ -2371,7 +2275,7 @@
         <v/>
       </c>
       <c r="AV14" t="str">
-        <f>IF($B14=730,SUM($G14-(SUM($H14:$I14))),"")</f>
+        <f>IF($B14=735,SUM($G14-(SUM($H14:$I14))),"")</f>
         <v/>
       </c>
     </row>
@@ -2509,18 +2413,6 @@
         <f>IF($B15=737,SUM($G15-(SUM($H15:$I15))),"")</f>
         <v/>
       </c>
-      <c r="AK15" t="str">
-        <f>IF($B15=725,SUM($G15-(SUM($H15:$I15))),"")</f>
-        <v/>
-      </c>
-      <c r="AL15" t="str">
-        <f>IF($B15=735,SUM($G15-(SUM($H15:$I15))),"")</f>
-        <v/>
-      </c>
-      <c r="AM15" t="str">
-        <f>IF($B15=727,SUM($G15-(SUM($H15:$I15))),"")</f>
-        <v/>
-      </c>
       <c r="AN15" t="str">
         <f>IF($B15=718,SUM($G15-(SUM($H15:$I15))),"")</f>
         <v/>
@@ -2554,7 +2446,7 @@
         <v/>
       </c>
       <c r="AV15" t="str">
-        <f>IF($B15=730,SUM($G15-(SUM($H15:$I15))),"")</f>
+        <f>IF($B15=735,SUM($G15-(SUM($H15:$I15))),"")</f>
         <v/>
       </c>
     </row>
@@ -2688,18 +2580,6 @@
         <f>IF($B16=737,SUM($G16-(SUM($H16:$I16))),"")</f>
         <v/>
       </c>
-      <c r="AK16" t="str">
-        <f>IF($B16=725,SUM($G16-(SUM($H16:$I16))),"")</f>
-        <v/>
-      </c>
-      <c r="AL16" t="str">
-        <f>IF($B16=735,SUM($G16-(SUM($H16:$I16))),"")</f>
-        <v/>
-      </c>
-      <c r="AM16" t="str">
-        <f>IF($B16=727,SUM($G16-(SUM($H16:$I16))),"")</f>
-        <v/>
-      </c>
       <c r="AN16" t="str">
         <f>IF($B16=718,SUM($G16-(SUM($H16:$I16))),"")</f>
         <v/>
@@ -2733,7 +2613,7 @@
         <v/>
       </c>
       <c r="AV16" t="str">
-        <f>IF($B16=730,SUM($G16-(SUM($H16:$I16))),"")</f>
+        <f>IF($B16=735,SUM($G16-(SUM($H16:$I16))),"")</f>
         <v/>
       </c>
     </row>
@@ -2867,18 +2747,6 @@
         <f>IF($B17=737,SUM($G17-(SUM($H17:$I17))),"")</f>
         <v/>
       </c>
-      <c r="AK17" t="str">
-        <f>IF($B17=725,SUM($G17-(SUM($H17:$I17))),"")</f>
-        <v/>
-      </c>
-      <c r="AL17" t="str">
-        <f>IF($B17=735,SUM($G17-(SUM($H17:$I17))),"")</f>
-        <v/>
-      </c>
-      <c r="AM17" t="str">
-        <f>IF($B17=727,SUM($G17-(SUM($H17:$I17))),"")</f>
-        <v/>
-      </c>
       <c r="AN17" t="str">
         <f>IF($B17=718,SUM($G17-(SUM($H17:$I17))),"")</f>
         <v/>
@@ -2912,7 +2780,7 @@
         <v/>
       </c>
       <c r="AV17" t="str">
-        <f>IF($B17=730,SUM($G17-(SUM($H17:$I17))),"")</f>
+        <f>IF($B17=735,SUM($G17-(SUM($H17:$I17))),"")</f>
         <v/>
       </c>
     </row>
@@ -3050,18 +2918,6 @@
         <f>IF($B18=737,SUM($G18-(SUM($H18:$I18))),"")</f>
         <v/>
       </c>
-      <c r="AK18" t="str">
-        <f>IF($B18=725,SUM($G18-(SUM($H18:$I18))),"")</f>
-        <v/>
-      </c>
-      <c r="AL18" t="str">
-        <f>IF($B18=735,SUM($G18-(SUM($H18:$I18))),"")</f>
-        <v/>
-      </c>
-      <c r="AM18" t="str">
-        <f>IF($B18=727,SUM($G18-(SUM($H18:$I18))),"")</f>
-        <v/>
-      </c>
       <c r="AN18" t="str">
         <f>IF($B18=718,SUM($G18-(SUM($H18:$I18))),"")</f>
         <v/>
@@ -3095,7 +2951,7 @@
         <v/>
       </c>
       <c r="AV18" t="str">
-        <f>IF($B18=730,SUM($G18-(SUM($H18:$I18))),"")</f>
+        <f>IF($B18=735,SUM($G18-(SUM($H18:$I18))),"")</f>
         <v/>
       </c>
     </row>
@@ -3233,18 +3089,6 @@
         <f>IF($B19=737,SUM($G19-(SUM($H19:$I19))),"")</f>
         <v/>
       </c>
-      <c r="AK19" t="str">
-        <f>IF($B19=725,SUM($G19-(SUM($H19:$I19))),"")</f>
-        <v/>
-      </c>
-      <c r="AL19" t="str">
-        <f>IF($B19=735,SUM($G19-(SUM($H19:$I19))),"")</f>
-        <v/>
-      </c>
-      <c r="AM19" t="str">
-        <f>IF($B19=727,SUM($G19-(SUM($H19:$I19))),"")</f>
-        <v/>
-      </c>
       <c r="AN19" t="str">
         <f>IF($B19=718,SUM($G19-(SUM($H19:$I19))),"")</f>
         <v/>
@@ -3278,7 +3122,7 @@
         <v/>
       </c>
       <c r="AV19" t="str">
-        <f>IF($B19=730,SUM($G19-(SUM($H19:$I19))),"")</f>
+        <f>IF($B19=735,SUM($G19-(SUM($H19:$I19))),"")</f>
         <v/>
       </c>
     </row>
@@ -3415,18 +3259,6 @@
         <f>IF($B20=737,SUM($G20-(SUM($H20:$I20))),"")</f>
         <v/>
       </c>
-      <c r="AK20" t="str">
-        <f>IF($B20=725,SUM($G20-(SUM($H20:$I20))),"")</f>
-        <v/>
-      </c>
-      <c r="AL20" t="str">
-        <f>IF($B20=735,SUM($G20-(SUM($H20:$I20))),"")</f>
-        <v/>
-      </c>
-      <c r="AM20" t="str">
-        <f>IF($B20=727,SUM($G20-(SUM($H20:$I20))),"")</f>
-        <v/>
-      </c>
       <c r="AN20" t="str">
         <f>IF($B20=718,SUM($G20-(SUM($H20:$I20))),"")</f>
         <v/>
@@ -3460,7 +3292,7 @@
         <v/>
       </c>
       <c r="AV20" t="str">
-        <f>IF($B20=730,SUM($G20-(SUM($H20:$I20))),"")</f>
+        <f>IF($B20=735,SUM($G20-(SUM($H20:$I20))),"")</f>
         <v/>
       </c>
     </row>
@@ -3597,18 +3429,6 @@
         <f>IF($B21=737,SUM($G21-(SUM($H21:$I21))),"")</f>
         <v/>
       </c>
-      <c r="AK21" t="str">
-        <f>IF($B21=725,SUM($G21-(SUM($H21:$I21))),"")</f>
-        <v/>
-      </c>
-      <c r="AL21" t="str">
-        <f>IF($B21=735,SUM($G21-(SUM($H21:$I21))),"")</f>
-        <v/>
-      </c>
-      <c r="AM21" t="str">
-        <f>IF($B21=727,SUM($G21-(SUM($H21:$I21))),"")</f>
-        <v/>
-      </c>
       <c r="AN21" t="str">
         <f>IF($B21=718,SUM($G21-(SUM($H21:$I21))),"")</f>
         <v/>
@@ -3642,7 +3462,7 @@
         <v/>
       </c>
       <c r="AV21" t="str">
-        <f>IF($B21=730,SUM($G21-(SUM($H21:$I21))),"")</f>
+        <f>IF($B21=735,SUM($G21-(SUM($H21:$I21))),"")</f>
         <v/>
       </c>
     </row>
@@ -3780,18 +3600,6 @@
         <f>IF($B22=737,SUM($G22-(SUM($H22:$I22))),"")</f>
         <v/>
       </c>
-      <c r="AK22" t="str">
-        <f>IF($B22=725,SUM($G22-(SUM($H22:$I22))),"")</f>
-        <v/>
-      </c>
-      <c r="AL22" t="str">
-        <f>IF($B22=735,SUM($G22-(SUM($H22:$I22))),"")</f>
-        <v/>
-      </c>
-      <c r="AM22" t="str">
-        <f>IF($B22=727,SUM($G22-(SUM($H22:$I22))),"")</f>
-        <v/>
-      </c>
       <c r="AN22" t="str">
         <f>IF($B22=718,SUM($G22-(SUM($H22:$I22))),"")</f>
         <v/>
@@ -3824,9 +3632,9 @@
         <f>IF($B22=731,SUM($G22-(SUM($H22:$I22))),"")</f>
         <v/>
       </c>
-      <c r="AV22" t="n">
-        <f>IF($B22=730,SUM($G22-(SUM($H22:$I22))),"")</f>
-        <v>0.0</v>
+      <c r="AV22" t="str">
+        <f>IF($B22=735,SUM($G22-(SUM($H22:$I22))),"")</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -3954,18 +3762,6 @@
         <f>IF($B23=737,SUM($G23-(SUM($H23:$I23))),"")</f>
         <v/>
       </c>
-      <c r="AK23" t="str" s="0">
-        <f>IF($B23=725,SUM($G23-(SUM($H23:$I23))),"")</f>
-        <v/>
-      </c>
-      <c r="AL23" t="str" s="0">
-        <f>IF($B23=735,SUM($G23-(SUM($H23:$I23))),"")</f>
-        <v/>
-      </c>
-      <c r="AM23" t="str" s="0">
-        <f>IF($B23=727,SUM($G23-(SUM($H23:$I23))),"")</f>
-        <v/>
-      </c>
       <c r="AN23" t="str" s="0">
         <f>IF($B23=718,SUM($G23-(SUM($H23:$I23))),"")</f>
         <v/>
@@ -3999,7 +3795,7 @@
         <v/>
       </c>
       <c r="AV23" t="str" s="0">
-        <f>IF($B23=730,SUM($G23-(SUM($H23:$I23))),"")</f>
+        <f>IF($B23=735,SUM($G23-(SUM($H23:$I23))),"")</f>
         <v/>
       </c>
     </row>
@@ -4137,18 +3933,6 @@
         <f>IF($B24=737,SUM($G24-(SUM($H24:$I24))),"")</f>
         <v/>
       </c>
-      <c r="AK24" t="str">
-        <f>IF($B24=725,SUM($G24-(SUM($H24:$I24))),"")</f>
-        <v/>
-      </c>
-      <c r="AL24" t="str">
-        <f>IF($B24=735,SUM($G24-(SUM($H24:$I24))),"")</f>
-        <v/>
-      </c>
-      <c r="AM24" t="str">
-        <f>IF($B24=727,SUM($G24-(SUM($H24:$I24))),"")</f>
-        <v/>
-      </c>
       <c r="AN24" t="str">
         <f>IF($B24=718,SUM($G24-(SUM($H24:$I24))),"")</f>
         <v/>
@@ -4182,7 +3966,7 @@
         <v/>
       </c>
       <c r="AV24" t="str">
-        <f>IF($B24=730,SUM($G24-(SUM($H24:$I24))),"")</f>
+        <f>IF($B24=735,SUM($G24-(SUM($H24:$I24))),"")</f>
         <v/>
       </c>
     </row>
@@ -4320,18 +4104,6 @@
         <f>IF($B25=737,SUM($G25-(SUM($H25:$I25))),"")</f>
         <v/>
       </c>
-      <c r="AK25" t="n">
-        <f>IF($B25=725,SUM($G25-(SUM($H25:$I25))),"")</f>
-        <v>0.0</v>
-      </c>
-      <c r="AL25" t="str">
-        <f>IF($B25=735,SUM($G25-(SUM($H25:$I25))),"")</f>
-        <v/>
-      </c>
-      <c r="AM25" t="str">
-        <f>IF($B25=727,SUM($G25-(SUM($H25:$I25))),"")</f>
-        <v/>
-      </c>
       <c r="AN25" t="str">
         <f>IF($B25=718,SUM($G25-(SUM($H25:$I25))),"")</f>
         <v/>
@@ -4365,7 +4137,7 @@
         <v/>
       </c>
       <c r="AV25" t="str">
-        <f>IF($B25=730,SUM($G25-(SUM($H25:$I25))),"")</f>
+        <f>IF($B25=735,SUM($G25-(SUM($H25:$I25))),"")</f>
         <v/>
       </c>
     </row>
@@ -4504,18 +4276,6 @@
         <f>IF($B26=737,SUM($G26-(SUM($H26:$I26))),"")</f>
         <v/>
       </c>
-      <c r="AK26" t="str">
-        <f>IF($B26=725,SUM($G26-(SUM($H26:$I26))),"")</f>
-        <v/>
-      </c>
-      <c r="AL26" t="str">
-        <f>IF($B26=735,SUM($G26-(SUM($H26:$I26))),"")</f>
-        <v/>
-      </c>
-      <c r="AM26" t="str">
-        <f>IF($B26=727,SUM($G26-(SUM($H26:$I26))),"")</f>
-        <v/>
-      </c>
       <c r="AN26" t="str">
         <f>IF($B26=718,SUM($G26-(SUM($H26:$I26))),"")</f>
         <v/>
@@ -4549,7 +4309,7 @@
         <v/>
       </c>
       <c r="AV26" t="str">
-        <f>IF($B26=730,SUM($G26-(SUM($H26:$I26))),"")</f>
+        <f>IF($B26=735,SUM($G26-(SUM($H26:$I26))),"")</f>
         <v/>
       </c>
     </row>
@@ -4687,18 +4447,6 @@
         <f>IF($B27=737,SUM($G27-(SUM($H27:$I27))),"")</f>
         <v/>
       </c>
-      <c r="AK27" t="str">
-        <f>IF($B27=725,SUM($G27-(SUM($H27:$I27))),"")</f>
-        <v/>
-      </c>
-      <c r="AL27" t="str">
-        <f>IF($B27=735,SUM($G27-(SUM($H27:$I27))),"")</f>
-        <v/>
-      </c>
-      <c r="AM27" t="n">
-        <f>IF($B27=727,SUM($G27-(SUM($H27:$I27))),"")</f>
-        <v>0.0</v>
-      </c>
       <c r="AN27" t="str">
         <f>IF($B27=718,SUM($G27-(SUM($H27:$I27))),"")</f>
         <v/>
@@ -4732,7 +4480,7 @@
         <v/>
       </c>
       <c r="AV27" t="str">
-        <f>IF($B27=730,SUM($G27-(SUM($H27:$I27))),"")</f>
+        <f>IF($B27=735,SUM($G27-(SUM($H27:$I27))),"")</f>
         <v/>
       </c>
     </row>
@@ -4870,18 +4618,6 @@
         <f>IF($B28=737,SUM($G28-(SUM($H28:$I28))),"")</f>
         <v/>
       </c>
-      <c r="AK28" t="str">
-        <f>IF($B28=725,SUM($G28-(SUM($H28:$I28))),"")</f>
-        <v/>
-      </c>
-      <c r="AL28" t="str">
-        <f>IF($B28=735,SUM($G28-(SUM($H28:$I28))),"")</f>
-        <v/>
-      </c>
-      <c r="AM28" t="str">
-        <f>IF($B28=727,SUM($G28-(SUM($H28:$I28))),"")</f>
-        <v/>
-      </c>
       <c r="AN28" t="str">
         <f>IF($B28=718,SUM($G28-(SUM($H28:$I28))),"")</f>
         <v/>
@@ -4915,7 +4651,7 @@
         <v/>
       </c>
       <c r="AV28" t="str">
-        <f>IF($B28=730,SUM($G28-(SUM($H28:$I28))),"")</f>
+        <f>IF($B28=735,SUM($G28-(SUM($H28:$I28))),"")</f>
         <v/>
       </c>
     </row>
@@ -5053,18 +4789,6 @@
         <f>IF($B29=737,SUM($G29-(SUM($H29:$I29))),"")</f>
         <v/>
       </c>
-      <c r="AK29" t="str">
-        <f>IF($B29=725,SUM($G29-(SUM($H29:$I29))),"")</f>
-        <v/>
-      </c>
-      <c r="AL29" t="str">
-        <f>IF($B29=735,SUM($G29-(SUM($H29:$I29))),"")</f>
-        <v/>
-      </c>
-      <c r="AM29" t="str">
-        <f>IF($B29=727,SUM($G29-(SUM($H29:$I29))),"")</f>
-        <v/>
-      </c>
       <c r="AN29" t="str">
         <f>IF($B29=718,SUM($G29-(SUM($H29:$I29))),"")</f>
         <v/>
@@ -5098,7 +4822,7 @@
         <v/>
       </c>
       <c r="AV29" t="str">
-        <f>IF($B29=730,SUM($G29-(SUM($H29:$I29))),"")</f>
+        <f>IF($B29=735,SUM($G29-(SUM($H29:$I29))),"")</f>
         <v/>
       </c>
     </row>
@@ -5236,18 +4960,6 @@
         <f>IF($B30=737,SUM($G30-(SUM($H30:$I30))),"")</f>
         <v/>
       </c>
-      <c r="AK30" t="str">
-        <f>IF($B30=725,SUM($G30-(SUM($H30:$I30))),"")</f>
-        <v/>
-      </c>
-      <c r="AL30" t="str">
-        <f>IF($B30=735,SUM($G30-(SUM($H30:$I30))),"")</f>
-        <v/>
-      </c>
-      <c r="AM30" t="str">
-        <f>IF($B30=727,SUM($G30-(SUM($H30:$I30))),"")</f>
-        <v/>
-      </c>
       <c r="AN30" t="str">
         <f>IF($B30=718,SUM($G30-(SUM($H30:$I30))),"")</f>
         <v/>
@@ -5281,7 +4993,7 @@
         <v/>
       </c>
       <c r="AV30" t="str">
-        <f>IF($B30=730,SUM($G30-(SUM($H30:$I30))),"")</f>
+        <f>IF($B30=735,SUM($G30-(SUM($H30:$I30))),"")</f>
         <v/>
       </c>
     </row>
@@ -5415,18 +5127,6 @@
         <f>IF($B31=737,SUM($G31-(SUM($H31:$I31))),"")</f>
         <v/>
       </c>
-      <c r="AK31" t="str">
-        <f>IF($B31=725,SUM($G31-(SUM($H31:$I31))),"")</f>
-        <v/>
-      </c>
-      <c r="AL31" t="str">
-        <f>IF($B31=735,SUM($G31-(SUM($H31:$I31))),"")</f>
-        <v/>
-      </c>
-      <c r="AM31" t="str">
-        <f>IF($B31=727,SUM($G31-(SUM($H31:$I31))),"")</f>
-        <v/>
-      </c>
       <c r="AN31" t="str">
         <f>IF($B31=718,SUM($G31-(SUM($H31:$I31))),"")</f>
         <v/>
@@ -5460,7 +5160,7 @@
         <v/>
       </c>
       <c r="AV31" t="str">
-        <f>IF($B31=730,SUM($G31-(SUM($H31:$I31))),"")</f>
+        <f>IF($B31=735,SUM($G31-(SUM($H31:$I31))),"")</f>
         <v/>
       </c>
     </row>
@@ -5594,18 +5294,6 @@
         <f>IF($B32=737,SUM($G32-(SUM($H32:$I32))),"")</f>
         <v/>
       </c>
-      <c r="AK32" t="str">
-        <f>IF($B32=725,SUM($G32-(SUM($H32:$I32))),"")</f>
-        <v/>
-      </c>
-      <c r="AL32" t="str">
-        <f>IF($B32=735,SUM($G32-(SUM($H32:$I32))),"")</f>
-        <v/>
-      </c>
-      <c r="AM32" t="str">
-        <f>IF($B32=727,SUM($G32-(SUM($H32:$I32))),"")</f>
-        <v/>
-      </c>
       <c r="AN32" t="str">
         <f>IF($B32=718,SUM($G32-(SUM($H32:$I32))),"")</f>
         <v/>
@@ -5639,7 +5327,7 @@
         <v/>
       </c>
       <c r="AV32" t="str">
-        <f>IF($B32=730,SUM($G32-(SUM($H32:$I32))),"")</f>
+        <f>IF($B32=735,SUM($G32-(SUM($H32:$I32))),"")</f>
         <v/>
       </c>
     </row>
@@ -5777,18 +5465,6 @@
         <f>IF($B33=737,SUM($G33-(SUM($H33:$I33))),"")</f>
         <v/>
       </c>
-      <c r="AK33" t="str">
-        <f>IF($B33=725,SUM($G33-(SUM($H33:$I33))),"")</f>
-        <v/>
-      </c>
-      <c r="AL33" t="str">
-        <f>IF($B33=735,SUM($G33-(SUM($H33:$I33))),"")</f>
-        <v/>
-      </c>
-      <c r="AM33" t="str">
-        <f>IF($B33=727,SUM($G33-(SUM($H33:$I33))),"")</f>
-        <v/>
-      </c>
       <c r="AN33" t="str">
         <f>IF($B33=718,SUM($G33-(SUM($H33:$I33))),"")</f>
         <v/>
@@ -5821,9 +5497,9 @@
         <f>IF($B33=731,SUM($G33-(SUM($H33:$I33))),"")</f>
         <v/>
       </c>
-      <c r="AV33" t="n">
-        <f>IF($B33=730,SUM($G33-(SUM($H33:$I33))),"")</f>
-        <v>0.0</v>
+      <c r="AV33" t="str">
+        <f>IF($B33=735,SUM($G33-(SUM($H33:$I33))),"")</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -5960,18 +5636,6 @@
         <f>IF($B34=737,SUM($G34-(SUM($H34:$I34))),"")</f>
         <v/>
       </c>
-      <c r="AK34" t="str">
-        <f>IF($B34=725,SUM($G34-(SUM($H34:$I34))),"")</f>
-        <v/>
-      </c>
-      <c r="AL34" t="str">
-        <f>IF($B34=735,SUM($G34-(SUM($H34:$I34))),"")</f>
-        <v/>
-      </c>
-      <c r="AM34" t="str">
-        <f>IF($B34=727,SUM($G34-(SUM($H34:$I34))),"")</f>
-        <v/>
-      </c>
       <c r="AN34" t="str">
         <f>IF($B34=718,SUM($G34-(SUM($H34:$I34))),"")</f>
         <v/>
@@ -6005,7 +5669,7 @@
         <v/>
       </c>
       <c r="AV34" t="str">
-        <f>IF($B34=730,SUM($G34-(SUM($H34:$I34))),"")</f>
+        <f>IF($B34=735,SUM($G34-(SUM($H34:$I34))),"")</f>
         <v/>
       </c>
     </row>
@@ -6143,18 +5807,6 @@
         <f>IF($B35=737,SUM($G35-(SUM($H35:$I35))),"")</f>
         <v/>
       </c>
-      <c r="AK35" t="str">
-        <f>IF($B35=725,SUM($G35-(SUM($H35:$I35))),"")</f>
-        <v/>
-      </c>
-      <c r="AL35" t="str">
-        <f>IF($B35=735,SUM($G35-(SUM($H35:$I35))),"")</f>
-        <v/>
-      </c>
-      <c r="AM35" t="str">
-        <f>IF($B35=727,SUM($G35-(SUM($H35:$I35))),"")</f>
-        <v/>
-      </c>
       <c r="AN35" t="str">
         <f>IF($B35=718,SUM($G35-(SUM($H35:$I35))),"")</f>
         <v/>
@@ -6188,7 +5840,7 @@
         <v/>
       </c>
       <c r="AV35" t="str">
-        <f>IF($B35=730,SUM($G35-(SUM($H35:$I35))),"")</f>
+        <f>IF($B35=735,SUM($G35-(SUM($H35:$I35))),"")</f>
         <v/>
       </c>
     </row>
@@ -6325,18 +5977,6 @@
         <f>IF($B36=737,SUM($G36-(SUM($H36:$I36))),"")</f>
         <v/>
       </c>
-      <c r="AK36" t="str">
-        <f>IF($B36=725,SUM($G36-(SUM($H36:$I36))),"")</f>
-        <v/>
-      </c>
-      <c r="AL36" t="str">
-        <f>IF($B36=735,SUM($G36-(SUM($H36:$I36))),"")</f>
-        <v/>
-      </c>
-      <c r="AM36" t="str">
-        <f>IF($B36=727,SUM($G36-(SUM($H36:$I36))),"")</f>
-        <v/>
-      </c>
       <c r="AN36" t="str">
         <f>IF($B36=718,SUM($G36-(SUM($H36:$I36))),"")</f>
         <v/>
@@ -6370,7 +6010,7 @@
         <v/>
       </c>
       <c r="AV36" t="str">
-        <f>IF($B36=730,SUM($G36-(SUM($H36:$I36))),"")</f>
+        <f>IF($B36=735,SUM($G36-(SUM($H36:$I36))),"")</f>
         <v/>
       </c>
     </row>
@@ -6508,18 +6148,6 @@
         <f>IF($B37=737,SUM($G37-(SUM($H37:$I37))),"")</f>
         <v/>
       </c>
-      <c r="AK37" t="str">
-        <f>IF($B37=725,SUM($G37-(SUM($H37:$I37))),"")</f>
-        <v/>
-      </c>
-      <c r="AL37" t="str">
-        <f>IF($B37=735,SUM($G37-(SUM($H37:$I37))),"")</f>
-        <v/>
-      </c>
-      <c r="AM37" t="str">
-        <f>IF($B37=727,SUM($G37-(SUM($H37:$I37))),"")</f>
-        <v/>
-      </c>
       <c r="AN37" t="str">
         <f>IF($B37=718,SUM($G37-(SUM($H37:$I37))),"")</f>
         <v/>
@@ -6553,7 +6181,7 @@
         <v/>
       </c>
       <c r="AV37" t="str">
-        <f>IF($B37=730,SUM($G37-(SUM($H37:$I37))),"")</f>
+        <f>IF($B37=735,SUM($G37-(SUM($H37:$I37))),"")</f>
         <v/>
       </c>
     </row>
@@ -6682,18 +6310,6 @@
         <f>IF($B38=737,SUM($G38-(SUM($H38:$I38))),"")</f>
         <v/>
       </c>
-      <c r="AK38" t="str" s="0">
-        <f>IF($B38=725,SUM($G38-(SUM($H38:$I38))),"")</f>
-        <v/>
-      </c>
-      <c r="AL38" t="str" s="0">
-        <f>IF($B38=735,SUM($G38-(SUM($H38:$I38))),"")</f>
-        <v/>
-      </c>
-      <c r="AM38" t="str" s="0">
-        <f>IF($B38=727,SUM($G38-(SUM($H38:$I38))),"")</f>
-        <v/>
-      </c>
       <c r="AN38" t="str" s="0">
         <f>IF($B38=718,SUM($G38-(SUM($H38:$I38))),"")</f>
         <v/>
@@ -6727,7 +6343,7 @@
         <v/>
       </c>
       <c r="AV38" t="str" s="0">
-        <f>IF($B38=730,SUM($G38-(SUM($H38:$I38))),"")</f>
+        <f>IF($B38=735,SUM($G38-(SUM($H38:$I38))),"")</f>
         <v/>
       </c>
     </row>
@@ -6865,18 +6481,6 @@
         <f>IF($B39=737,SUM($G39-(SUM($H39:$I39))),"")</f>
         <v/>
       </c>
-      <c r="AK39" t="str">
-        <f>IF($B39=725,SUM($G39-(SUM($H39:$I39))),"")</f>
-        <v/>
-      </c>
-      <c r="AL39" t="str">
-        <f>IF($B39=735,SUM($G39-(SUM($H39:$I39))),"")</f>
-        <v/>
-      </c>
-      <c r="AM39" t="str">
-        <f>IF($B39=727,SUM($G39-(SUM($H39:$I39))),"")</f>
-        <v/>
-      </c>
       <c r="AN39" t="str">
         <f>IF($B39=718,SUM($G39-(SUM($H39:$I39))),"")</f>
         <v/>
@@ -6910,7 +6514,7 @@
         <v/>
       </c>
       <c r="AV39" t="str">
-        <f>IF($B39=730,SUM($G39-(SUM($H39:$I39))),"")</f>
+        <f>IF($B39=735,SUM($G39-(SUM($H39:$I39))),"")</f>
         <v/>
       </c>
     </row>
@@ -7049,18 +6653,6 @@
         <f>IF($B40=737,SUM($G40-(SUM($H40:$I40))),"")</f>
         <v/>
       </c>
-      <c r="AK40" t="str">
-        <f>IF($B40=725,SUM($G40-(SUM($H40:$I40))),"")</f>
-        <v/>
-      </c>
-      <c r="AL40" t="str">
-        <f>IF($B40=735,SUM($G40-(SUM($H40:$I40))),"")</f>
-        <v/>
-      </c>
-      <c r="AM40" t="str">
-        <f>IF($B40=727,SUM($G40-(SUM($H40:$I40))),"")</f>
-        <v/>
-      </c>
       <c r="AN40" t="str">
         <f>IF($B40=718,SUM($G40-(SUM($H40:$I40))),"")</f>
         <v/>
@@ -7094,7 +6686,7 @@
         <v/>
       </c>
       <c r="AV40" t="str">
-        <f>IF($B40=730,SUM($G40-(SUM($H40:$I40))),"")</f>
+        <f>IF($B40=735,SUM($G40-(SUM($H40:$I40))),"")</f>
         <v/>
       </c>
     </row>
@@ -7232,18 +6824,6 @@
         <f>IF($B41=737,SUM($G41-(SUM($H41:$I41))),"")</f>
         <v/>
       </c>
-      <c r="AK41" t="n">
-        <f>IF($B41=725,SUM($G41-(SUM($H41:$I41))),"")</f>
-        <v>0.0</v>
-      </c>
-      <c r="AL41" t="str">
-        <f>IF($B41=735,SUM($G41-(SUM($H41:$I41))),"")</f>
-        <v/>
-      </c>
-      <c r="AM41" t="str">
-        <f>IF($B41=727,SUM($G41-(SUM($H41:$I41))),"")</f>
-        <v/>
-      </c>
       <c r="AN41" t="str">
         <f>IF($B41=718,SUM($G41-(SUM($H41:$I41))),"")</f>
         <v/>
@@ -7277,7 +6857,7 @@
         <v/>
       </c>
       <c r="AV41" t="str">
-        <f>IF($B41=730,SUM($G41-(SUM($H41:$I41))),"")</f>
+        <f>IF($B41=735,SUM($G41-(SUM($H41:$I41))),"")</f>
         <v/>
       </c>
     </row>
@@ -7415,18 +6995,6 @@
         <f>IF($B42=737,SUM($G42-(SUM($H42:$I42))),"")</f>
         <v/>
       </c>
-      <c r="AK42" t="str">
-        <f>IF($B42=725,SUM($G42-(SUM($H42:$I42))),"")</f>
-        <v/>
-      </c>
-      <c r="AL42" t="str">
-        <f>IF($B42=735,SUM($G42-(SUM($H42:$I42))),"")</f>
-        <v/>
-      </c>
-      <c r="AM42" t="str">
-        <f>IF($B42=727,SUM($G42-(SUM($H42:$I42))),"")</f>
-        <v/>
-      </c>
       <c r="AN42" t="str">
         <f>IF($B42=718,SUM($G42-(SUM($H42:$I42))),"")</f>
         <v/>
@@ -7460,7 +7028,7 @@
         <v/>
       </c>
       <c r="AV42" t="str">
-        <f>IF($B42=730,SUM($G42-(SUM($H42:$I42))),"")</f>
+        <f>IF($B42=735,SUM($G42-(SUM($H42:$I42))),"")</f>
         <v/>
       </c>
     </row>
@@ -7598,18 +7166,6 @@
         <f>IF($B43=737,SUM($G43-(SUM($H43:$I43))),"")</f>
         <v/>
       </c>
-      <c r="AK43" t="str">
-        <f>IF($B43=725,SUM($G43-(SUM($H43:$I43))),"")</f>
-        <v/>
-      </c>
-      <c r="AL43" t="str">
-        <f>IF($B43=735,SUM($G43-(SUM($H43:$I43))),"")</f>
-        <v/>
-      </c>
-      <c r="AM43" t="n">
-        <f>IF($B43=727,SUM($G43-(SUM($H43:$I43))),"")</f>
-        <v>0.0</v>
-      </c>
       <c r="AN43" t="str">
         <f>IF($B43=718,SUM($G43-(SUM($H43:$I43))),"")</f>
         <v/>
@@ -7643,7 +7199,7 @@
         <v/>
       </c>
       <c r="AV43" t="str">
-        <f>IF($B43=730,SUM($G43-(SUM($H43:$I43))),"")</f>
+        <f>IF($B43=735,SUM($G43-(SUM($H43:$I43))),"")</f>
         <v/>
       </c>
     </row>
@@ -7781,18 +7337,6 @@
         <f>IF($B44=737,SUM($G44-(SUM($H44:$I44))),"")</f>
         <v/>
       </c>
-      <c r="AK44" t="str">
-        <f>IF($B44=725,SUM($G44-(SUM($H44:$I44))),"")</f>
-        <v/>
-      </c>
-      <c r="AL44" t="str">
-        <f>IF($B44=735,SUM($G44-(SUM($H44:$I44))),"")</f>
-        <v/>
-      </c>
-      <c r="AM44" t="str">
-        <f>IF($B44=727,SUM($G44-(SUM($H44:$I44))),"")</f>
-        <v/>
-      </c>
       <c r="AN44" t="str">
         <f>IF($B44=718,SUM($G44-(SUM($H44:$I44))),"")</f>
         <v/>
@@ -7826,7 +7370,7 @@
         <v/>
       </c>
       <c r="AV44" t="str">
-        <f>IF($B44=730,SUM($G44-(SUM($H44:$I44))),"")</f>
+        <f>IF($B44=735,SUM($G44-(SUM($H44:$I44))),"")</f>
         <v/>
       </c>
     </row>
@@ -7964,18 +7508,6 @@
         <f>IF($B45=737,SUM($G45-(SUM($H45:$I45))),"")</f>
         <v/>
       </c>
-      <c r="AK45" t="str">
-        <f>IF($B45=725,SUM($G45-(SUM($H45:$I45))),"")</f>
-        <v/>
-      </c>
-      <c r="AL45" t="str">
-        <f>IF($B45=735,SUM($G45-(SUM($H45:$I45))),"")</f>
-        <v/>
-      </c>
-      <c r="AM45" t="str">
-        <f>IF($B45=727,SUM($G45-(SUM($H45:$I45))),"")</f>
-        <v/>
-      </c>
       <c r="AN45" t="str">
         <f>IF($B45=718,SUM($G45-(SUM($H45:$I45))),"")</f>
         <v/>
@@ -8009,7 +7541,7 @@
         <v/>
       </c>
       <c r="AV45" t="str">
-        <f>IF($B45=730,SUM($G45-(SUM($H45:$I45))),"")</f>
+        <f>IF($B45=735,SUM($G45-(SUM($H45:$I45))),"")</f>
         <v/>
       </c>
     </row>
@@ -8147,18 +7679,6 @@
         <f>IF($B46=737,SUM($G46-(SUM($H46:$I46))),"")</f>
         <v/>
       </c>
-      <c r="AK46" t="str">
-        <f>IF($B46=725,SUM($G46-(SUM($H46:$I46))),"")</f>
-        <v/>
-      </c>
-      <c r="AL46" t="str">
-        <f>IF($B46=735,SUM($G46-(SUM($H46:$I46))),"")</f>
-        <v/>
-      </c>
-      <c r="AM46" t="str">
-        <f>IF($B46=727,SUM($G46-(SUM($H46:$I46))),"")</f>
-        <v/>
-      </c>
       <c r="AN46" t="str">
         <f>IF($B46=718,SUM($G46-(SUM($H46:$I46))),"")</f>
         <v/>
@@ -8192,7 +7712,7 @@
         <v/>
       </c>
       <c r="AV46" t="str">
-        <f>IF($B46=730,SUM($G46-(SUM($H46:$I46))),"")</f>
+        <f>IF($B46=735,SUM($G46-(SUM($H46:$I46))),"")</f>
         <v/>
       </c>
     </row>
@@ -8330,18 +7850,6 @@
         <f>IF($B47=737,SUM($G47-(SUM($H47:$I47))),"")</f>
         <v/>
       </c>
-      <c r="AK47" t="str">
-        <f>IF($B47=725,SUM($G47-(SUM($H47:$I47))),"")</f>
-        <v/>
-      </c>
-      <c r="AL47" t="str">
-        <f>IF($B47=735,SUM($G47-(SUM($H47:$I47))),"")</f>
-        <v/>
-      </c>
-      <c r="AM47" t="str">
-        <f>IF($B47=727,SUM($G47-(SUM($H47:$I47))),"")</f>
-        <v/>
-      </c>
       <c r="AN47" t="str">
         <f>IF($B47=718,SUM($G47-(SUM($H47:$I47))),"")</f>
         <v/>
@@ -8375,7 +7883,7 @@
         <v/>
       </c>
       <c r="AV47" t="str">
-        <f>IF($B47=730,SUM($G47-(SUM($H47:$I47))),"")</f>
+        <f>IF($B47=735,SUM($G47-(SUM($H47:$I47))),"")</f>
         <v/>
       </c>
     </row>
@@ -8513,18 +8021,6 @@
         <f>IF($B48=737,SUM($G48-(SUM($H48:$I48))),"")</f>
         <v/>
       </c>
-      <c r="AK48" t="str">
-        <f>IF($B48=725,SUM($G48-(SUM($H48:$I48))),"")</f>
-        <v/>
-      </c>
-      <c r="AL48" t="str">
-        <f>IF($B48=735,SUM($G48-(SUM($H48:$I48))),"")</f>
-        <v/>
-      </c>
-      <c r="AM48" t="str">
-        <f>IF($B48=727,SUM($G48-(SUM($H48:$I48))),"")</f>
-        <v/>
-      </c>
       <c r="AN48" t="str">
         <f>IF($B48=718,SUM($G48-(SUM($H48:$I48))),"")</f>
         <v/>
@@ -8558,7 +8054,7 @@
         <v/>
       </c>
       <c r="AV48" t="str">
-        <f>IF($B48=730,SUM($G48-(SUM($H48:$I48))),"")</f>
+        <f>IF($B48=735,SUM($G48-(SUM($H48:$I48))),"")</f>
         <v/>
       </c>
     </row>
@@ -8696,18 +8192,6 @@
         <f>IF($B49=737,SUM($G49-(SUM($H49:$I49))),"")</f>
         <v/>
       </c>
-      <c r="AK49" t="str">
-        <f>IF($B49=725,SUM($G49-(SUM($H49:$I49))),"")</f>
-        <v/>
-      </c>
-      <c r="AL49" t="str">
-        <f>IF($B49=735,SUM($G49-(SUM($H49:$I49))),"")</f>
-        <v/>
-      </c>
-      <c r="AM49" t="str">
-        <f>IF($B49=727,SUM($G49-(SUM($H49:$I49))),"")</f>
-        <v/>
-      </c>
       <c r="AN49" t="str">
         <f>IF($B49=718,SUM($G49-(SUM($H49:$I49))),"")</f>
         <v/>
@@ -8741,7 +8225,7 @@
         <v/>
       </c>
       <c r="AV49" t="str">
-        <f>IF($B49=730,SUM($G49-(SUM($H49:$I49))),"")</f>
+        <f>IF($B49=735,SUM($G49-(SUM($H49:$I49))),"")</f>
         <v/>
       </c>
     </row>
@@ -8875,18 +8359,6 @@
         <f>IF($B50=737,SUM($G50-(SUM($H50:$I50))),"")</f>
         <v/>
       </c>
-      <c r="AK50" t="str">
-        <f>IF($B50=725,SUM($G50-(SUM($H50:$I50))),"")</f>
-        <v/>
-      </c>
-      <c r="AL50" t="str">
-        <f>IF($B50=735,SUM($G50-(SUM($H50:$I50))),"")</f>
-        <v/>
-      </c>
-      <c r="AM50" t="str">
-        <f>IF($B50=727,SUM($G50-(SUM($H50:$I50))),"")</f>
-        <v/>
-      </c>
       <c r="AN50" t="str">
         <f>IF($B50=718,SUM($G50-(SUM($H50:$I50))),"")</f>
         <v/>
@@ -8920,7 +8392,7 @@
         <v/>
       </c>
       <c r="AV50" t="str">
-        <f>IF($B50=730,SUM($G50-(SUM($H50:$I50))),"")</f>
+        <f>IF($B50=735,SUM($G50-(SUM($H50:$I50))),"")</f>
         <v/>
       </c>
     </row>
@@ -9054,18 +8526,6 @@
         <f>IF($B51=737,SUM($G51-(SUM($H51:$I51))),"")</f>
         <v/>
       </c>
-      <c r="AK51" t="str">
-        <f>IF($B51=725,SUM($G51-(SUM($H51:$I51))),"")</f>
-        <v/>
-      </c>
-      <c r="AL51" t="str">
-        <f>IF($B51=735,SUM($G51-(SUM($H51:$I51))),"")</f>
-        <v/>
-      </c>
-      <c r="AM51" t="str">
-        <f>IF($B51=727,SUM($G51-(SUM($H51:$I51))),"")</f>
-        <v/>
-      </c>
       <c r="AN51" t="str">
         <f>IF($B51=718,SUM($G51-(SUM($H51:$I51))),"")</f>
         <v/>
@@ -9099,7 +8559,7 @@
         <v/>
       </c>
       <c r="AV51" t="str">
-        <f>IF($B51=730,SUM($G51-(SUM($H51:$I51))),"")</f>
+        <f>IF($B51=735,SUM($G51-(SUM($H51:$I51))),"")</f>
         <v/>
       </c>
     </row>
@@ -9236,18 +8696,6 @@
         <f>IF($B52=737,SUM($G52-(SUM($H52:$I52))),"")</f>
         <v/>
       </c>
-      <c r="AK52" t="str">
-        <f>IF($B52=725,SUM($G52-(SUM($H52:$I52))),"")</f>
-        <v/>
-      </c>
-      <c r="AL52" t="str">
-        <f>IF($B52=735,SUM($G52-(SUM($H52:$I52))),"")</f>
-        <v/>
-      </c>
-      <c r="AM52" t="str">
-        <f>IF($B52=727,SUM($G52-(SUM($H52:$I52))),"")</f>
-        <v/>
-      </c>
       <c r="AN52" t="str">
         <f>IF($B52=718,SUM($G52-(SUM($H52:$I52))),"")</f>
         <v/>
@@ -9281,7 +8729,7 @@
         <v/>
       </c>
       <c r="AV52" t="str">
-        <f>IF($B52=730,SUM($G52-(SUM($H52:$I52))),"")</f>
+        <f>IF($B52=735,SUM($G52-(SUM($H52:$I52))),"")</f>
         <v/>
       </c>
     </row>
@@ -9418,18 +8866,6 @@
         <f>IF($B53=737,SUM($G53-(SUM($H53:$I53))),"")</f>
         <v/>
       </c>
-      <c r="AK53" t="str">
-        <f>IF($B53=725,SUM($G53-(SUM($H53:$I53))),"")</f>
-        <v/>
-      </c>
-      <c r="AL53" t="str">
-        <f>IF($B53=735,SUM($G53-(SUM($H53:$I53))),"")</f>
-        <v/>
-      </c>
-      <c r="AM53" t="str">
-        <f>IF($B53=727,SUM($G53-(SUM($H53:$I53))),"")</f>
-        <v/>
-      </c>
       <c r="AN53" t="str">
         <f>IF($B53=718,SUM($G53-(SUM($H53:$I53))),"")</f>
         <v/>
@@ -9463,7 +8899,7 @@
         <v/>
       </c>
       <c r="AV53" t="str">
-        <f>IF($B53=730,SUM($G53-(SUM($H53:$I53))),"")</f>
+        <f>IF($B53=735,SUM($G53-(SUM($H53:$I53))),"")</f>
         <v/>
       </c>
     </row>
@@ -9601,18 +9037,6 @@
         <f>IF($B54=737,SUM($G54-(SUM($H54:$I54))),"")</f>
         <v/>
       </c>
-      <c r="AK54" t="str">
-        <f>IF($B54=725,SUM($G54-(SUM($H54:$I54))),"")</f>
-        <v/>
-      </c>
-      <c r="AL54" t="str">
-        <f>IF($B54=735,SUM($G54-(SUM($H54:$I54))),"")</f>
-        <v/>
-      </c>
-      <c r="AM54" t="str">
-        <f>IF($B54=727,SUM($G54-(SUM($H54:$I54))),"")</f>
-        <v/>
-      </c>
       <c r="AN54" t="str">
         <f>IF($B54=718,SUM($G54-(SUM($H54:$I54))),"")</f>
         <v/>
@@ -9646,7 +9070,7 @@
         <v/>
       </c>
       <c r="AV54" t="str">
-        <f>IF($B54=730,SUM($G54-(SUM($H54:$I54))),"")</f>
+        <f>IF($B54=735,SUM($G54-(SUM($H54:$I54))),"")</f>
         <v/>
       </c>
     </row>
@@ -9775,18 +9199,6 @@
         <f>IF($B55=737,SUM($G55-(SUM($H55:$I55))),"")</f>
         <v/>
       </c>
-      <c r="AK55" t="str" s="0">
-        <f>IF($B55=725,SUM($G55-(SUM($H55:$I55))),"")</f>
-        <v/>
-      </c>
-      <c r="AL55" t="str" s="0">
-        <f>IF($B55=735,SUM($G55-(SUM($H55:$I55))),"")</f>
-        <v/>
-      </c>
-      <c r="AM55" t="str" s="0">
-        <f>IF($B55=727,SUM($G55-(SUM($H55:$I55))),"")</f>
-        <v/>
-      </c>
       <c r="AN55" t="str" s="0">
         <f>IF($B55=718,SUM($G55-(SUM($H55:$I55))),"")</f>
         <v/>
@@ -9820,7 +9232,7 @@
         <v/>
       </c>
       <c r="AV55" t="str" s="0">
-        <f>IF($B55=730,SUM($G55-(SUM($H55:$I55))),"")</f>
+        <f>IF($B55=735,SUM($G55-(SUM($H55:$I55))),"")</f>
         <v/>
       </c>
     </row>
@@ -9958,18 +9370,6 @@
         <f>IF($B56=737,SUM($G56-(SUM($H56:$I56))),"")</f>
         <v/>
       </c>
-      <c r="AK56" t="str">
-        <f>IF($B56=725,SUM($G56-(SUM($H56:$I56))),"")</f>
-        <v/>
-      </c>
-      <c r="AL56" t="str">
-        <f>IF($B56=735,SUM($G56-(SUM($H56:$I56))),"")</f>
-        <v/>
-      </c>
-      <c r="AM56" t="str">
-        <f>IF($B56=727,SUM($G56-(SUM($H56:$I56))),"")</f>
-        <v/>
-      </c>
       <c r="AN56" t="str">
         <f>IF($B56=718,SUM($G56-(SUM($H56:$I56))),"")</f>
         <v/>
@@ -10003,7 +9403,7 @@
         <v/>
       </c>
       <c r="AV56" t="str">
-        <f>IF($B56=730,SUM($G56-(SUM($H56:$I56))),"")</f>
+        <f>IF($B56=735,SUM($G56-(SUM($H56:$I56))),"")</f>
         <v/>
       </c>
     </row>
@@ -10141,18 +9541,6 @@
         <f>IF($B57=737,SUM($G57-(SUM($H57:$I57))),"")</f>
         <v/>
       </c>
-      <c r="AK57" t="str">
-        <f>IF($B57=725,SUM($G57-(SUM($H57:$I57))),"")</f>
-        <v/>
-      </c>
-      <c r="AL57" t="str">
-        <f>IF($B57=735,SUM($G57-(SUM($H57:$I57))),"")</f>
-        <v/>
-      </c>
-      <c r="AM57" t="str">
-        <f>IF($B57=727,SUM($G57-(SUM($H57:$I57))),"")</f>
-        <v/>
-      </c>
       <c r="AN57" t="str">
         <f>IF($B57=718,SUM($G57-(SUM($H57:$I57))),"")</f>
         <v/>
@@ -10186,7 +9574,7 @@
         <v/>
       </c>
       <c r="AV57" t="str">
-        <f>IF($B57=730,SUM($G57-(SUM($H57:$I57))),"")</f>
+        <f>IF($B57=735,SUM($G57-(SUM($H57:$I57))),"")</f>
         <v/>
       </c>
     </row>
@@ -10324,18 +9712,6 @@
         <f>IF($B58=737,SUM($G58-(SUM($H58:$I58))),"")</f>
         <v/>
       </c>
-      <c r="AK58" t="n">
-        <f>IF($B58=725,SUM($G58-(SUM($H58:$I58))),"")</f>
-        <v>0.0</v>
-      </c>
-      <c r="AL58" t="str">
-        <f>IF($B58=735,SUM($G58-(SUM($H58:$I58))),"")</f>
-        <v/>
-      </c>
-      <c r="AM58" t="str">
-        <f>IF($B58=727,SUM($G58-(SUM($H58:$I58))),"")</f>
-        <v/>
-      </c>
       <c r="AN58" t="str">
         <f>IF($B58=718,SUM($G58-(SUM($H58:$I58))),"")</f>
         <v/>
@@ -10369,7 +9745,7 @@
         <v/>
       </c>
       <c r="AV58" t="str">
-        <f>IF($B58=730,SUM($G58-(SUM($H58:$I58))),"")</f>
+        <f>IF($B58=735,SUM($G58-(SUM($H58:$I58))),"")</f>
         <v/>
       </c>
     </row>
@@ -10508,18 +9884,6 @@
         <f>IF($B59=737,SUM($G59-(SUM($H59:$I59))),"")</f>
         <v/>
       </c>
-      <c r="AK59" t="str">
-        <f>IF($B59=725,SUM($G59-(SUM($H59:$I59))),"")</f>
-        <v/>
-      </c>
-      <c r="AL59" t="str">
-        <f>IF($B59=735,SUM($G59-(SUM($H59:$I59))),"")</f>
-        <v/>
-      </c>
-      <c r="AM59" t="str">
-        <f>IF($B59=727,SUM($G59-(SUM($H59:$I59))),"")</f>
-        <v/>
-      </c>
       <c r="AN59" t="str">
         <f>IF($B59=718,SUM($G59-(SUM($H59:$I59))),"")</f>
         <v/>
@@ -10553,7 +9917,7 @@
         <v/>
       </c>
       <c r="AV59" t="str">
-        <f>IF($B59=730,SUM($G59-(SUM($H59:$I59))),"")</f>
+        <f>IF($B59=735,SUM($G59-(SUM($H59:$I59))),"")</f>
         <v/>
       </c>
     </row>
@@ -10691,18 +10055,6 @@
         <f>IF($B60=737,SUM($G60-(SUM($H60:$I60))),"")</f>
         <v/>
       </c>
-      <c r="AK60" t="str">
-        <f>IF($B60=725,SUM($G60-(SUM($H60:$I60))),"")</f>
-        <v/>
-      </c>
-      <c r="AL60" t="str">
-        <f>IF($B60=735,SUM($G60-(SUM($H60:$I60))),"")</f>
-        <v/>
-      </c>
-      <c r="AM60" t="n">
-        <f>IF($B60=727,SUM($G60-(SUM($H60:$I60))),"")</f>
-        <v>0.0</v>
-      </c>
       <c r="AN60" t="str">
         <f>IF($B60=718,SUM($G60-(SUM($H60:$I60))),"")</f>
         <v/>
@@ -10736,7 +10088,7 @@
         <v/>
       </c>
       <c r="AV60" t="str">
-        <f>IF($B60=730,SUM($G60-(SUM($H60:$I60))),"")</f>
+        <f>IF($B60=735,SUM($G60-(SUM($H60:$I60))),"")</f>
         <v/>
       </c>
     </row>
@@ -10874,18 +10226,6 @@
         <f>IF($B61=737,SUM($G61-(SUM($H61:$I61))),"")</f>
         <v/>
       </c>
-      <c r="AK61" t="str">
-        <f>IF($B61=725,SUM($G61-(SUM($H61:$I61))),"")</f>
-        <v/>
-      </c>
-      <c r="AL61" t="str">
-        <f>IF($B61=735,SUM($G61-(SUM($H61:$I61))),"")</f>
-        <v/>
-      </c>
-      <c r="AM61" t="str">
-        <f>IF($B61=727,SUM($G61-(SUM($H61:$I61))),"")</f>
-        <v/>
-      </c>
       <c r="AN61" t="str">
         <f>IF($B61=718,SUM($G61-(SUM($H61:$I61))),"")</f>
         <v/>
@@ -10919,7 +10259,7 @@
         <v/>
       </c>
       <c r="AV61" t="str">
-        <f>IF($B61=730,SUM($G61-(SUM($H61:$I61))),"")</f>
+        <f>IF($B61=735,SUM($G61-(SUM($H61:$I61))),"")</f>
         <v/>
       </c>
     </row>
@@ -11057,18 +10397,6 @@
         <f>IF($B62=737,SUM($G62-(SUM($H62:$I62))),"")</f>
         <v/>
       </c>
-      <c r="AK62" t="str">
-        <f>IF($B62=725,SUM($G62-(SUM($H62:$I62))),"")</f>
-        <v/>
-      </c>
-      <c r="AL62" t="str">
-        <f>IF($B62=735,SUM($G62-(SUM($H62:$I62))),"")</f>
-        <v/>
-      </c>
-      <c r="AM62" t="str">
-        <f>IF($B62=727,SUM($G62-(SUM($H62:$I62))),"")</f>
-        <v/>
-      </c>
       <c r="AN62" t="str">
         <f>IF($B62=718,SUM($G62-(SUM($H62:$I62))),"")</f>
         <v/>
@@ -11102,7 +10430,7 @@
         <v/>
       </c>
       <c r="AV62" t="str">
-        <f>IF($B62=730,SUM($G62-(SUM($H62:$I62))),"")</f>
+        <f>IF($B62=735,SUM($G62-(SUM($H62:$I62))),"")</f>
         <v/>
       </c>
     </row>
@@ -11240,18 +10568,6 @@
         <f>IF($B63=737,SUM($G63-(SUM($H63:$I63))),"")</f>
         <v/>
       </c>
-      <c r="AK63" t="str">
-        <f>IF($B63=725,SUM($G63-(SUM($H63:$I63))),"")</f>
-        <v/>
-      </c>
-      <c r="AL63" t="str">
-        <f>IF($B63=735,SUM($G63-(SUM($H63:$I63))),"")</f>
-        <v/>
-      </c>
-      <c r="AM63" t="str">
-        <f>IF($B63=727,SUM($G63-(SUM($H63:$I63))),"")</f>
-        <v/>
-      </c>
       <c r="AN63" t="str">
         <f>IF($B63=718,SUM($G63-(SUM($H63:$I63))),"")</f>
         <v/>
@@ -11285,7 +10601,7 @@
         <v/>
       </c>
       <c r="AV63" t="str">
-        <f>IF($B63=730,SUM($G63-(SUM($H63:$I63))),"")</f>
+        <f>IF($B63=735,SUM($G63-(SUM($H63:$I63))),"")</f>
         <v/>
       </c>
     </row>
@@ -11423,18 +10739,6 @@
         <f>IF($B64=737,SUM($G64-(SUM($H64:$I64))),"")</f>
         <v/>
       </c>
-      <c r="AK64" t="str">
-        <f>IF($B64=725,SUM($G64-(SUM($H64:$I64))),"")</f>
-        <v/>
-      </c>
-      <c r="AL64" t="str">
-        <f>IF($B64=735,SUM($G64-(SUM($H64:$I64))),"")</f>
-        <v/>
-      </c>
-      <c r="AM64" t="str">
-        <f>IF($B64=727,SUM($G64-(SUM($H64:$I64))),"")</f>
-        <v/>
-      </c>
       <c r="AN64" t="str">
         <f>IF($B64=718,SUM($G64-(SUM($H64:$I64))),"")</f>
         <v/>
@@ -11468,7 +10772,7 @@
         <v/>
       </c>
       <c r="AV64" t="str">
-        <f>IF($B64=730,SUM($G64-(SUM($H64:$I64))),"")</f>
+        <f>IF($B64=735,SUM($G64-(SUM($H64:$I64))),"")</f>
         <v/>
       </c>
     </row>
@@ -11606,18 +10910,6 @@
         <f>IF($B65=737,SUM($G65-(SUM($H65:$I65))),"")</f>
         <v/>
       </c>
-      <c r="AK65" t="str">
-        <f>IF($B65=725,SUM($G65-(SUM($H65:$I65))),"")</f>
-        <v/>
-      </c>
-      <c r="AL65" t="str">
-        <f>IF($B65=735,SUM($G65-(SUM($H65:$I65))),"")</f>
-        <v/>
-      </c>
-      <c r="AM65" t="str">
-        <f>IF($B65=727,SUM($G65-(SUM($H65:$I65))),"")</f>
-        <v/>
-      </c>
       <c r="AN65" t="str">
         <f>IF($B65=718,SUM($G65-(SUM($H65:$I65))),"")</f>
         <v/>
@@ -11651,7 +10943,7 @@
         <v/>
       </c>
       <c r="AV65" t="str">
-        <f>IF($B65=730,SUM($G65-(SUM($H65:$I65))),"")</f>
+        <f>IF($B65=735,SUM($G65-(SUM($H65:$I65))),"")</f>
         <v/>
       </c>
     </row>
@@ -11789,18 +11081,6 @@
         <f>IF($B66=737,SUM($G66-(SUM($H66:$I66))),"")</f>
         <v/>
       </c>
-      <c r="AK66" t="str">
-        <f>IF($B66=725,SUM($G66-(SUM($H66:$I66))),"")</f>
-        <v/>
-      </c>
-      <c r="AL66" t="str">
-        <f>IF($B66=735,SUM($G66-(SUM($H66:$I66))),"")</f>
-        <v/>
-      </c>
-      <c r="AM66" t="str">
-        <f>IF($B66=727,SUM($G66-(SUM($H66:$I66))),"")</f>
-        <v/>
-      </c>
       <c r="AN66" t="str">
         <f>IF($B66=718,SUM($G66-(SUM($H66:$I66))),"")</f>
         <v/>
@@ -11834,7 +11114,7 @@
         <v/>
       </c>
       <c r="AV66" t="str">
-        <f>IF($B66=730,SUM($G66-(SUM($H66:$I66))),"")</f>
+        <f>IF($B66=735,SUM($G66-(SUM($H66:$I66))),"")</f>
         <v/>
       </c>
     </row>
@@ -11968,18 +11248,6 @@
         <f>IF($B67=737,SUM($G67-(SUM($H67:$I67))),"")</f>
         <v/>
       </c>
-      <c r="AK67" t="str">
-        <f>IF($B67=725,SUM($G67-(SUM($H67:$I67))),"")</f>
-        <v/>
-      </c>
-      <c r="AL67" t="str">
-        <f>IF($B67=735,SUM($G67-(SUM($H67:$I67))),"")</f>
-        <v/>
-      </c>
-      <c r="AM67" t="str">
-        <f>IF($B67=727,SUM($G67-(SUM($H67:$I67))),"")</f>
-        <v/>
-      </c>
       <c r="AN67" t="str">
         <f>IF($B67=718,SUM($G67-(SUM($H67:$I67))),"")</f>
         <v/>
@@ -12013,7 +11281,7 @@
         <v/>
       </c>
       <c r="AV67" t="str">
-        <f>IF($B67=730,SUM($G67-(SUM($H67:$I67))),"")</f>
+        <f>IF($B67=735,SUM($G67-(SUM($H67:$I67))),"")</f>
         <v/>
       </c>
     </row>
@@ -12150,18 +11418,6 @@
         <f>IF($B68=737,SUM($G68-(SUM($H68:$I68))),"")</f>
         <v/>
       </c>
-      <c r="AK68" t="str">
-        <f>IF($B68=725,SUM($G68-(SUM($H68:$I68))),"")</f>
-        <v/>
-      </c>
-      <c r="AL68" t="str">
-        <f>IF($B68=735,SUM($G68-(SUM($H68:$I68))),"")</f>
-        <v/>
-      </c>
-      <c r="AM68" t="str">
-        <f>IF($B68=727,SUM($G68-(SUM($H68:$I68))),"")</f>
-        <v/>
-      </c>
       <c r="AN68" t="str">
         <f>IF($B68=718,SUM($G68-(SUM($H68:$I68))),"")</f>
         <v/>
@@ -12195,7 +11451,7 @@
         <v/>
       </c>
       <c r="AV68" t="str">
-        <f>IF($B68=730,SUM($G68-(SUM($H68:$I68))),"")</f>
+        <f>IF($B68=735,SUM($G68-(SUM($H68:$I68))),"")</f>
         <v/>
       </c>
     </row>
@@ -12332,18 +11588,6 @@
         <f>IF($B69=737,SUM($G69-(SUM($H69:$I69))),"")</f>
         <v/>
       </c>
-      <c r="AK69" t="str">
-        <f>IF($B69=725,SUM($G69-(SUM($H69:$I69))),"")</f>
-        <v/>
-      </c>
-      <c r="AL69" t="str">
-        <f>IF($B69=735,SUM($G69-(SUM($H69:$I69))),"")</f>
-        <v/>
-      </c>
-      <c r="AM69" t="str">
-        <f>IF($B69=727,SUM($G69-(SUM($H69:$I69))),"")</f>
-        <v/>
-      </c>
       <c r="AN69" t="str">
         <f>IF($B69=718,SUM($G69-(SUM($H69:$I69))),"")</f>
         <v/>
@@ -12377,7 +11621,7 @@
         <v/>
       </c>
       <c r="AV69" t="str">
-        <f>IF($B69=730,SUM($G69-(SUM($H69:$I69))),"")</f>
+        <f>IF($B69=735,SUM($G69-(SUM($H69:$I69))),"")</f>
         <v/>
       </c>
     </row>
@@ -12515,18 +11759,6 @@
         <f>IF($B70=737,SUM($G70-(SUM($H70:$I70))),"")</f>
         <v/>
       </c>
-      <c r="AK70" t="str">
-        <f>IF($B70=725,SUM($G70-(SUM($H70:$I70))),"")</f>
-        <v/>
-      </c>
-      <c r="AL70" t="str">
-        <f>IF($B70=735,SUM($G70-(SUM($H70:$I70))),"")</f>
-        <v/>
-      </c>
-      <c r="AM70" t="str">
-        <f>IF($B70=727,SUM($G70-(SUM($H70:$I70))),"")</f>
-        <v/>
-      </c>
       <c r="AN70" t="str">
         <f>IF($B70=718,SUM($G70-(SUM($H70:$I70))),"")</f>
         <v/>
@@ -12560,7 +11792,7 @@
         <v/>
       </c>
       <c r="AV70" t="str">
-        <f>IF($B70=730,SUM($G70-(SUM($H70:$I70))),"")</f>
+        <f>IF($B70=735,SUM($G70-(SUM($H70:$I70))),"")</f>
         <v/>
       </c>
     </row>
@@ -12689,18 +11921,6 @@
         <f>IF($B71=737,SUM($G71-(SUM($H71:$I71))),"")</f>
         <v/>
       </c>
-      <c r="AK71" t="str" s="0">
-        <f>IF($B71=725,SUM($G71-(SUM($H71:$I71))),"")</f>
-        <v/>
-      </c>
-      <c r="AL71" t="str" s="0">
-        <f>IF($B71=735,SUM($G71-(SUM($H71:$I71))),"")</f>
-        <v/>
-      </c>
-      <c r="AM71" t="str" s="0">
-        <f>IF($B71=727,SUM($G71-(SUM($H71:$I71))),"")</f>
-        <v/>
-      </c>
       <c r="AN71" t="str" s="0">
         <f>IF($B71=718,SUM($G71-(SUM($H71:$I71))),"")</f>
         <v/>
@@ -12734,7 +11954,7 @@
         <v/>
       </c>
       <c r="AV71" t="str" s="0">
-        <f>IF($B71=730,SUM($G71-(SUM($H71:$I71))),"")</f>
+        <f>IF($B71=735,SUM($G71-(SUM($H71:$I71))),"")</f>
         <v/>
       </c>
     </row>
@@ -12872,18 +12092,6 @@
         <f>IF($B72=737,SUM($G72-(SUM($H72:$I72))),"")</f>
         <v/>
       </c>
-      <c r="AK72" t="str">
-        <f>IF($B72=725,SUM($G72-(SUM($H72:$I72))),"")</f>
-        <v/>
-      </c>
-      <c r="AL72" t="str">
-        <f>IF($B72=735,SUM($G72-(SUM($H72:$I72))),"")</f>
-        <v/>
-      </c>
-      <c r="AM72" t="str">
-        <f>IF($B72=727,SUM($G72-(SUM($H72:$I72))),"")</f>
-        <v/>
-      </c>
       <c r="AN72" t="str">
         <f>IF($B72=718,SUM($G72-(SUM($H72:$I72))),"")</f>
         <v/>
@@ -12917,7 +12125,7 @@
         <v/>
       </c>
       <c r="AV72" t="str">
-        <f>IF($B72=730,SUM($G72-(SUM($H72:$I72))),"")</f>
+        <f>IF($B72=735,SUM($G72-(SUM($H72:$I72))),"")</f>
         <v/>
       </c>
     </row>
@@ -13055,18 +12263,6 @@
         <f>IF($B73=737,SUM($G73-(SUM($H73:$I73))),"")</f>
         <v/>
       </c>
-      <c r="AK73" t="n">
-        <f>IF($B73=725,SUM($G73-(SUM($H73:$I73))),"")</f>
-        <v>0.0</v>
-      </c>
-      <c r="AL73" t="str">
-        <f>IF($B73=735,SUM($G73-(SUM($H73:$I73))),"")</f>
-        <v/>
-      </c>
-      <c r="AM73" t="str">
-        <f>IF($B73=727,SUM($G73-(SUM($H73:$I73))),"")</f>
-        <v/>
-      </c>
       <c r="AN73" t="str">
         <f>IF($B73=718,SUM($G73-(SUM($H73:$I73))),"")</f>
         <v/>
@@ -13100,7 +12296,7 @@
         <v/>
       </c>
       <c r="AV73" t="str">
-        <f>IF($B73=730,SUM($G73-(SUM($H73:$I73))),"")</f>
+        <f>IF($B73=735,SUM($G73-(SUM($H73:$I73))),"")</f>
         <v/>
       </c>
     </row>
@@ -13239,18 +12435,6 @@
         <f>IF($B74=737,SUM($G74-(SUM($H74:$I74))),"")</f>
         <v/>
       </c>
-      <c r="AK74" t="str">
-        <f>IF($B74=725,SUM($G74-(SUM($H74:$I74))),"")</f>
-        <v/>
-      </c>
-      <c r="AL74" t="str">
-        <f>IF($B74=735,SUM($G74-(SUM($H74:$I74))),"")</f>
-        <v/>
-      </c>
-      <c r="AM74" t="str">
-        <f>IF($B74=727,SUM($G74-(SUM($H74:$I74))),"")</f>
-        <v/>
-      </c>
       <c r="AN74" t="str">
         <f>IF($B74=718,SUM($G74-(SUM($H74:$I74))),"")</f>
         <v/>
@@ -13284,7 +12468,7 @@
         <v/>
       </c>
       <c r="AV74" t="str">
-        <f>IF($B74=730,SUM($G74-(SUM($H74:$I74))),"")</f>
+        <f>IF($B74=735,SUM($G74-(SUM($H74:$I74))),"")</f>
         <v/>
       </c>
     </row>
@@ -13422,18 +12606,6 @@
         <f>IF($B75=737,SUM($G75-(SUM($H75:$I75))),"")</f>
         <v/>
       </c>
-      <c r="AK75" t="str">
-        <f>IF($B75=725,SUM($G75-(SUM($H75:$I75))),"")</f>
-        <v/>
-      </c>
-      <c r="AL75" t="str">
-        <f>IF($B75=735,SUM($G75-(SUM($H75:$I75))),"")</f>
-        <v/>
-      </c>
-      <c r="AM75" t="str">
-        <f>IF($B75=727,SUM($G75-(SUM($H75:$I75))),"")</f>
-        <v/>
-      </c>
       <c r="AN75" t="str">
         <f>IF($B75=718,SUM($G75-(SUM($H75:$I75))),"")</f>
         <v/>
@@ -13466,9 +12638,9 @@
         <f>IF($B75=731,SUM($G75-(SUM($H75:$I75))),"")</f>
         <v/>
       </c>
-      <c r="AV75" t="n">
-        <f>IF($B75=730,SUM($G75-(SUM($H75:$I75))),"")</f>
-        <v>0.0</v>
+      <c r="AV75" t="str">
+        <f>IF($B75=735,SUM($G75-(SUM($H75:$I75))),"")</f>
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -13605,18 +12777,6 @@
         <f>IF($B76=737,SUM($G76-(SUM($H76:$I76))),"")</f>
         <v/>
       </c>
-      <c r="AK76" t="str">
-        <f>IF($B76=725,SUM($G76-(SUM($H76:$I76))),"")</f>
-        <v/>
-      </c>
-      <c r="AL76" t="str">
-        <f>IF($B76=735,SUM($G76-(SUM($H76:$I76))),"")</f>
-        <v/>
-      </c>
-      <c r="AM76" t="n">
-        <f>IF($B76=727,SUM($G76-(SUM($H76:$I76))),"")</f>
-        <v>0.0</v>
-      </c>
       <c r="AN76" t="str">
         <f>IF($B76=718,SUM($G76-(SUM($H76:$I76))),"")</f>
         <v/>
@@ -13650,7 +12810,7 @@
         <v/>
       </c>
       <c r="AV76" t="str">
-        <f>IF($B76=730,SUM($G76-(SUM($H76:$I76))),"")</f>
+        <f>IF($B76=735,SUM($G76-(SUM($H76:$I76))),"")</f>
         <v/>
       </c>
     </row>
@@ -13788,18 +12948,6 @@
         <f>IF($B77=737,SUM($G77-(SUM($H77:$I77))),"")</f>
         <v/>
       </c>
-      <c r="AK77" t="str">
-        <f>IF($B77=725,SUM($G77-(SUM($H77:$I77))),"")</f>
-        <v/>
-      </c>
-      <c r="AL77" t="str">
-        <f>IF($B77=735,SUM($G77-(SUM($H77:$I77))),"")</f>
-        <v/>
-      </c>
-      <c r="AM77" t="str">
-        <f>IF($B77=727,SUM($G77-(SUM($H77:$I77))),"")</f>
-        <v/>
-      </c>
       <c r="AN77" t="str">
         <f>IF($B77=718,SUM($G77-(SUM($H77:$I77))),"")</f>
         <v/>
@@ -13833,7 +12981,7 @@
         <v/>
       </c>
       <c r="AV77" t="str">
-        <f>IF($B77=730,SUM($G77-(SUM($H77:$I77))),"")</f>
+        <f>IF($B77=735,SUM($G77-(SUM($H77:$I77))),"")</f>
         <v/>
       </c>
     </row>
@@ -13971,18 +13119,6 @@
         <f>IF($B78=737,SUM($G78-(SUM($H78:$I78))),"")</f>
         <v/>
       </c>
-      <c r="AK78" t="str">
-        <f>IF($B78=725,SUM($G78-(SUM($H78:$I78))),"")</f>
-        <v/>
-      </c>
-      <c r="AL78" t="str">
-        <f>IF($B78=735,SUM($G78-(SUM($H78:$I78))),"")</f>
-        <v/>
-      </c>
-      <c r="AM78" t="str">
-        <f>IF($B78=727,SUM($G78-(SUM($H78:$I78))),"")</f>
-        <v/>
-      </c>
       <c r="AN78" t="str">
         <f>IF($B78=718,SUM($G78-(SUM($H78:$I78))),"")</f>
         <v/>
@@ -14016,7 +13152,7 @@
         <v/>
       </c>
       <c r="AV78" t="str">
-        <f>IF($B78=730,SUM($G78-(SUM($H78:$I78))),"")</f>
+        <f>IF($B78=735,SUM($G78-(SUM($H78:$I78))),"")</f>
         <v/>
       </c>
     </row>
@@ -14154,18 +13290,6 @@
         <f>IF($B79=737,SUM($G79-(SUM($H79:$I79))),"")</f>
         <v/>
       </c>
-      <c r="AK79" t="str">
-        <f>IF($B79=725,SUM($G79-(SUM($H79:$I79))),"")</f>
-        <v/>
-      </c>
-      <c r="AL79" t="str">
-        <f>IF($B79=735,SUM($G79-(SUM($H79:$I79))),"")</f>
-        <v/>
-      </c>
-      <c r="AM79" t="str">
-        <f>IF($B79=727,SUM($G79-(SUM($H79:$I79))),"")</f>
-        <v/>
-      </c>
       <c r="AN79" t="str">
         <f>IF($B79=718,SUM($G79-(SUM($H79:$I79))),"")</f>
         <v/>
@@ -14199,7 +13323,7 @@
         <v/>
       </c>
       <c r="AV79" t="str">
-        <f>IF($B79=730,SUM($G79-(SUM($H79:$I79))),"")</f>
+        <f>IF($B79=735,SUM($G79-(SUM($H79:$I79))),"")</f>
         <v/>
       </c>
     </row>
@@ -14337,18 +13461,6 @@
         <f>IF($B80=737,SUM($G80-(SUM($H80:$I80))),"")</f>
         <v/>
       </c>
-      <c r="AK80" t="str">
-        <f>IF($B80=725,SUM($G80-(SUM($H80:$I80))),"")</f>
-        <v/>
-      </c>
-      <c r="AL80" t="str">
-        <f>IF($B80=735,SUM($G80-(SUM($H80:$I80))),"")</f>
-        <v/>
-      </c>
-      <c r="AM80" t="str">
-        <f>IF($B80=727,SUM($G80-(SUM($H80:$I80))),"")</f>
-        <v/>
-      </c>
       <c r="AN80" t="str">
         <f>IF($B80=718,SUM($G80-(SUM($H80:$I80))),"")</f>
         <v/>
@@ -14382,7 +13494,7 @@
         <v/>
       </c>
       <c r="AV80" t="str">
-        <f>IF($B80=730,SUM($G80-(SUM($H80:$I80))),"")</f>
+        <f>IF($B80=735,SUM($G80-(SUM($H80:$I80))),"")</f>
         <v/>
       </c>
     </row>
@@ -14520,18 +13632,6 @@
         <f>IF($B81=737,SUM($G81-(SUM($H81:$I81))),"")</f>
         <v/>
       </c>
-      <c r="AK81" t="str">
-        <f>IF($B81=725,SUM($G81-(SUM($H81:$I81))),"")</f>
-        <v/>
-      </c>
-      <c r="AL81" t="str">
-        <f>IF($B81=735,SUM($G81-(SUM($H81:$I81))),"")</f>
-        <v/>
-      </c>
-      <c r="AM81" t="str">
-        <f>IF($B81=727,SUM($G81-(SUM($H81:$I81))),"")</f>
-        <v/>
-      </c>
       <c r="AN81" t="str">
         <f>IF($B81=718,SUM($G81-(SUM($H81:$I81))),"")</f>
         <v/>
@@ -14565,7 +13665,7 @@
         <v/>
       </c>
       <c r="AV81" t="str">
-        <f>IF($B81=730,SUM($G81-(SUM($H81:$I81))),"")</f>
+        <f>IF($B81=735,SUM($G81-(SUM($H81:$I81))),"")</f>
         <v/>
       </c>
     </row>
@@ -14703,18 +13803,6 @@
         <f>IF($B82=737,SUM($G82-(SUM($H82:$I82))),"")</f>
         <v/>
       </c>
-      <c r="AK82" t="str">
-        <f>IF($B82=725,SUM($G82-(SUM($H82:$I82))),"")</f>
-        <v/>
-      </c>
-      <c r="AL82" t="str">
-        <f>IF($B82=735,SUM($G82-(SUM($H82:$I82))),"")</f>
-        <v/>
-      </c>
-      <c r="AM82" t="str">
-        <f>IF($B82=727,SUM($G82-(SUM($H82:$I82))),"")</f>
-        <v/>
-      </c>
       <c r="AN82" t="str">
         <f>IF($B82=718,SUM($G82-(SUM($H82:$I82))),"")</f>
         <v/>
@@ -14748,7 +13836,7 @@
         <v/>
       </c>
       <c r="AV82" t="str">
-        <f>IF($B82=730,SUM($G82-(SUM($H82:$I82))),"")</f>
+        <f>IF($B82=735,SUM($G82-(SUM($H82:$I82))),"")</f>
         <v/>
       </c>
     </row>
@@ -14882,18 +13970,6 @@
         <f>IF($B83=737,SUM($G83-(SUM($H83:$I83))),"")</f>
         <v/>
       </c>
-      <c r="AK83" t="str">
-        <f>IF($B83=725,SUM($G83-(SUM($H83:$I83))),"")</f>
-        <v/>
-      </c>
-      <c r="AL83" t="str">
-        <f>IF($B83=735,SUM($G83-(SUM($H83:$I83))),"")</f>
-        <v/>
-      </c>
-      <c r="AM83" t="str">
-        <f>IF($B83=727,SUM($G83-(SUM($H83:$I83))),"")</f>
-        <v/>
-      </c>
       <c r="AN83" t="str">
         <f>IF($B83=718,SUM($G83-(SUM($H83:$I83))),"")</f>
         <v/>
@@ -14927,7 +14003,7 @@
         <v/>
       </c>
       <c r="AV83" t="str">
-        <f>IF($B83=730,SUM($G83-(SUM($H83:$I83))),"")</f>
+        <f>IF($B83=735,SUM($G83-(SUM($H83:$I83))),"")</f>
         <v/>
       </c>
     </row>
@@ -15061,18 +14137,6 @@
         <f>IF($B84=737,SUM($G84-(SUM($H84:$I84))),"")</f>
         <v/>
       </c>
-      <c r="AK84" t="str">
-        <f>IF($B84=725,SUM($G84-(SUM($H84:$I84))),"")</f>
-        <v/>
-      </c>
-      <c r="AL84" t="str">
-        <f>IF($B84=735,SUM($G84-(SUM($H84:$I84))),"")</f>
-        <v/>
-      </c>
-      <c r="AM84" t="str">
-        <f>IF($B84=727,SUM($G84-(SUM($H84:$I84))),"")</f>
-        <v/>
-      </c>
       <c r="AN84" t="str">
         <f>IF($B84=718,SUM($G84-(SUM($H84:$I84))),"")</f>
         <v/>
@@ -15106,7 +14170,7 @@
         <v/>
       </c>
       <c r="AV84" t="str">
-        <f>IF($B84=730,SUM($G84-(SUM($H84:$I84))),"")</f>
+        <f>IF($B84=735,SUM($G84-(SUM($H84:$I84))),"")</f>
         <v/>
       </c>
     </row>
@@ -15244,18 +14308,6 @@
         <f>IF($B85=737,SUM($G85-(SUM($H85:$I85))),"")</f>
         <v/>
       </c>
-      <c r="AK85" t="str">
-        <f>IF($B85=725,SUM($G85-(SUM($H85:$I85))),"")</f>
-        <v/>
-      </c>
-      <c r="AL85" t="str">
-        <f>IF($B85=735,SUM($G85-(SUM($H85:$I85))),"")</f>
-        <v/>
-      </c>
-      <c r="AM85" t="str">
-        <f>IF($B85=727,SUM($G85-(SUM($H85:$I85))),"")</f>
-        <v/>
-      </c>
       <c r="AN85" t="str">
         <f>IF($B85=718,SUM($G85-(SUM($H85:$I85))),"")</f>
         <v/>
@@ -15289,7 +14341,7 @@
         <v/>
       </c>
       <c r="AV85" t="str">
-        <f>IF($B85=730,SUM($G85-(SUM($H85:$I85))),"")</f>
+        <f>IF($B85=735,SUM($G85-(SUM($H85:$I85))),"")</f>
         <v/>
       </c>
     </row>
@@ -15426,18 +14478,6 @@
         <f>IF($B86=737,SUM($G86-(SUM($H86:$I86))),"")</f>
         <v/>
       </c>
-      <c r="AK86" t="str">
-        <f>IF($B86=725,SUM($G86-(SUM($H86:$I86))),"")</f>
-        <v/>
-      </c>
-      <c r="AL86" t="str">
-        <f>IF($B86=735,SUM($G86-(SUM($H86:$I86))),"")</f>
-        <v/>
-      </c>
-      <c r="AM86" t="str">
-        <f>IF($B86=727,SUM($G86-(SUM($H86:$I86))),"")</f>
-        <v/>
-      </c>
       <c r="AN86" t="str">
         <f>IF($B86=718,SUM($G86-(SUM($H86:$I86))),"")</f>
         <v/>
@@ -15471,7 +14511,7 @@
         <v/>
       </c>
       <c r="AV86" t="str">
-        <f>IF($B86=730,SUM($G86-(SUM($H86:$I86))),"")</f>
+        <f>IF($B86=735,SUM($G86-(SUM($H86:$I86))),"")</f>
         <v/>
       </c>
     </row>
@@ -15600,18 +14640,6 @@
         <f>IF($B87=737,SUM($G87-(SUM($H87:$I87))),"")</f>
         <v/>
       </c>
-      <c r="AK87" t="str" s="0">
-        <f>IF($B87=725,SUM($G87-(SUM($H87:$I87))),"")</f>
-        <v/>
-      </c>
-      <c r="AL87" t="str" s="0">
-        <f>IF($B87=735,SUM($G87-(SUM($H87:$I87))),"")</f>
-        <v/>
-      </c>
-      <c r="AM87" t="str" s="0">
-        <f>IF($B87=727,SUM($G87-(SUM($H87:$I87))),"")</f>
-        <v/>
-      </c>
       <c r="AN87" t="str" s="0">
         <f>IF($B87=718,SUM($G87-(SUM($H87:$I87))),"")</f>
         <v/>
@@ -15645,7 +14673,7 @@
         <v/>
       </c>
       <c r="AV87" t="str" s="0">
-        <f>IF($B87=730,SUM($G87-(SUM($H87:$I87))),"")</f>
+        <f>IF($B87=735,SUM($G87-(SUM($H87:$I87))),"")</f>
         <v/>
       </c>
     </row>
@@ -15783,18 +14811,6 @@
         <f>IF($B88=737,SUM($G88-(SUM($H88:$I88))),"")</f>
         <v/>
       </c>
-      <c r="AK88" t="str">
-        <f>IF($B88=725,SUM($G88-(SUM($H88:$I88))),"")</f>
-        <v/>
-      </c>
-      <c r="AL88" t="str">
-        <f>IF($B88=735,SUM($G88-(SUM($H88:$I88))),"")</f>
-        <v/>
-      </c>
-      <c r="AM88" t="str">
-        <f>IF($B88=727,SUM($G88-(SUM($H88:$I88))),"")</f>
-        <v/>
-      </c>
       <c r="AN88" t="str">
         <f>IF($B88=718,SUM($G88-(SUM($H88:$I88))),"")</f>
         <v/>
@@ -15828,7 +14844,7 @@
         <v/>
       </c>
       <c r="AV88" t="str">
-        <f>IF($B88=730,SUM($G88-(SUM($H88:$I88))),"")</f>
+        <f>IF($B88=735,SUM($G88-(SUM($H88:$I88))),"")</f>
         <v/>
       </c>
     </row>
@@ -15966,18 +14982,6 @@
         <f>IF($B89=737,SUM($G89-(SUM($H89:$I89))),"")</f>
         <v/>
       </c>
-      <c r="AK89" t="n">
-        <f>IF($B89=725,SUM($G89-(SUM($H89:$I89))),"")</f>
-        <v>0.0</v>
-      </c>
-      <c r="AL89" t="str">
-        <f>IF($B89=735,SUM($G89-(SUM($H89:$I89))),"")</f>
-        <v/>
-      </c>
-      <c r="AM89" t="str">
-        <f>IF($B89=727,SUM($G89-(SUM($H89:$I89))),"")</f>
-        <v/>
-      </c>
       <c r="AN89" t="str">
         <f>IF($B89=718,SUM($G89-(SUM($H89:$I89))),"")</f>
         <v/>
@@ -16011,7 +15015,7 @@
         <v/>
       </c>
       <c r="AV89" t="str">
-        <f>IF($B89=730,SUM($G89-(SUM($H89:$I89))),"")</f>
+        <f>IF($B89=735,SUM($G89-(SUM($H89:$I89))),"")</f>
         <v/>
       </c>
     </row>
@@ -16150,18 +15154,6 @@
         <f>IF($B90=737,SUM($G90-(SUM($H90:$I90))),"")</f>
         <v/>
       </c>
-      <c r="AK90" t="str">
-        <f>IF($B90=725,SUM($G90-(SUM($H90:$I90))),"")</f>
-        <v/>
-      </c>
-      <c r="AL90" t="str">
-        <f>IF($B90=735,SUM($G90-(SUM($H90:$I90))),"")</f>
-        <v/>
-      </c>
-      <c r="AM90" t="str">
-        <f>IF($B90=727,SUM($G90-(SUM($H90:$I90))),"")</f>
-        <v/>
-      </c>
       <c r="AN90" t="str">
         <f>IF($B90=718,SUM($G90-(SUM($H90:$I90))),"")</f>
         <v/>
@@ -16195,7 +15187,7 @@
         <v/>
       </c>
       <c r="AV90" t="str">
-        <f>IF($B90=730,SUM($G90-(SUM($H90:$I90))),"")</f>
+        <f>IF($B90=735,SUM($G90-(SUM($H90:$I90))),"")</f>
         <v/>
       </c>
     </row>
@@ -16333,18 +15325,6 @@
         <f>IF($B91=737,SUM($G91-(SUM($H91:$I91))),"")</f>
         <v/>
       </c>
-      <c r="AK91" t="str">
-        <f>IF($B91=725,SUM($G91-(SUM($H91:$I91))),"")</f>
-        <v/>
-      </c>
-      <c r="AL91" t="str">
-        <f>IF($B91=735,SUM($G91-(SUM($H91:$I91))),"")</f>
-        <v/>
-      </c>
-      <c r="AM91" t="n">
-        <f>IF($B91=727,SUM($G91-(SUM($H91:$I91))),"")</f>
-        <v>0.0</v>
-      </c>
       <c r="AN91" t="str">
         <f>IF($B91=718,SUM($G91-(SUM($H91:$I91))),"")</f>
         <v/>
@@ -16378,7 +15358,7 @@
         <v/>
       </c>
       <c r="AV91" t="str">
-        <f>IF($B91=730,SUM($G91-(SUM($H91:$I91))),"")</f>
+        <f>IF($B91=735,SUM($G91-(SUM($H91:$I91))),"")</f>
         <v/>
       </c>
     </row>
@@ -16516,18 +15496,6 @@
         <f>IF($B92=737,SUM($G92-(SUM($H92:$I92))),"")</f>
         <v/>
       </c>
-      <c r="AK92" t="str">
-        <f>IF($B92=725,SUM($G92-(SUM($H92:$I92))),"")</f>
-        <v/>
-      </c>
-      <c r="AL92" t="str">
-        <f>IF($B92=735,SUM($G92-(SUM($H92:$I92))),"")</f>
-        <v/>
-      </c>
-      <c r="AM92" t="str">
-        <f>IF($B92=727,SUM($G92-(SUM($H92:$I92))),"")</f>
-        <v/>
-      </c>
       <c r="AN92" t="str">
         <f>IF($B92=718,SUM($G92-(SUM($H92:$I92))),"")</f>
         <v/>
@@ -16561,7 +15529,7 @@
         <v/>
       </c>
       <c r="AV92" t="str">
-        <f>IF($B92=730,SUM($G92-(SUM($H92:$I92))),"")</f>
+        <f>IF($B92=735,SUM($G92-(SUM($H92:$I92))),"")</f>
         <v/>
       </c>
     </row>
@@ -16699,18 +15667,6 @@
         <f>IF($B93=737,SUM($G93-(SUM($H93:$I93))),"")</f>
         <v/>
       </c>
-      <c r="AK93" t="str">
-        <f>IF($B93=725,SUM($G93-(SUM($H93:$I93))),"")</f>
-        <v/>
-      </c>
-      <c r="AL93" t="str">
-        <f>IF($B93=735,SUM($G93-(SUM($H93:$I93))),"")</f>
-        <v/>
-      </c>
-      <c r="AM93" t="str">
-        <f>IF($B93=727,SUM($G93-(SUM($H93:$I93))),"")</f>
-        <v/>
-      </c>
       <c r="AN93" t="str">
         <f>IF($B93=718,SUM($G93-(SUM($H93:$I93))),"")</f>
         <v/>
@@ -16744,7 +15700,7 @@
         <v/>
       </c>
       <c r="AV93" t="str">
-        <f>IF($B93=730,SUM($G93-(SUM($H93:$I93))),"")</f>
+        <f>IF($B93=735,SUM($G93-(SUM($H93:$I93))),"")</f>
         <v/>
       </c>
     </row>
@@ -16882,18 +15838,6 @@
         <f>IF($B94=737,SUM($G94-(SUM($H94:$I94))),"")</f>
         <v/>
       </c>
-      <c r="AK94" t="str">
-        <f>IF($B94=725,SUM($G94-(SUM($H94:$I94))),"")</f>
-        <v/>
-      </c>
-      <c r="AL94" t="str">
-        <f>IF($B94=735,SUM($G94-(SUM($H94:$I94))),"")</f>
-        <v/>
-      </c>
-      <c r="AM94" t="str">
-        <f>IF($B94=727,SUM($G94-(SUM($H94:$I94))),"")</f>
-        <v/>
-      </c>
       <c r="AN94" t="str">
         <f>IF($B94=718,SUM($G94-(SUM($H94:$I94))),"")</f>
         <v/>
@@ -16927,7 +15871,7 @@
         <v/>
       </c>
       <c r="AV94" t="str">
-        <f>IF($B94=730,SUM($G94-(SUM($H94:$I94))),"")</f>
+        <f>IF($B94=735,SUM($G94-(SUM($H94:$I94))),"")</f>
         <v/>
       </c>
     </row>
@@ -17062,18 +16006,6 @@
         <f>IF($B95=737,SUM($G95-(SUM($H95:$I95))),"")</f>
         <v/>
       </c>
-      <c r="AK95" t="str">
-        <f>IF($B95=725,SUM($G95-(SUM($H95:$I95))),"")</f>
-        <v/>
-      </c>
-      <c r="AL95" t="str">
-        <f>IF($B95=735,SUM($G95-(SUM($H95:$I95))),"")</f>
-        <v/>
-      </c>
-      <c r="AM95" t="str">
-        <f>IF($B95=727,SUM($G95-(SUM($H95:$I95))),"")</f>
-        <v/>
-      </c>
       <c r="AN95" t="str">
         <f>IF($B95=718,SUM($G95-(SUM($H95:$I95))),"")</f>
         <v/>
@@ -17107,7 +16039,7 @@
         <v/>
       </c>
       <c r="AV95" t="str">
-        <f>IF($B95=730,SUM($G95-(SUM($H95:$I95))),"")</f>
+        <f>IF($B95=735,SUM($G95-(SUM($H95:$I95))),"")</f>
         <v/>
       </c>
     </row>
@@ -17241,18 +16173,6 @@
         <f>IF($B96=737,SUM($G96-(SUM($H96:$I96))),"")</f>
         <v/>
       </c>
-      <c r="AK96" t="str">
-        <f>IF($B96=725,SUM($G96-(SUM($H96:$I96))),"")</f>
-        <v/>
-      </c>
-      <c r="AL96" t="str">
-        <f>IF($B96=735,SUM($G96-(SUM($H96:$I96))),"")</f>
-        <v/>
-      </c>
-      <c r="AM96" t="str">
-        <f>IF($B96=727,SUM($G96-(SUM($H96:$I96))),"")</f>
-        <v/>
-      </c>
       <c r="AN96" t="str">
         <f>IF($B96=718,SUM($G96-(SUM($H96:$I96))),"")</f>
         <v/>
@@ -17286,7 +16206,7 @@
         <v/>
       </c>
       <c r="AV96" t="str">
-        <f>IF($B96=730,SUM($G96-(SUM($H96:$I96))),"")</f>
+        <f>IF($B96=735,SUM($G96-(SUM($H96:$I96))),"")</f>
         <v/>
       </c>
     </row>
@@ -17424,18 +16344,6 @@
         <f>IF($B97=737,SUM($G97-(SUM($H97:$I97))),"")</f>
         <v/>
       </c>
-      <c r="AK97" t="str">
-        <f>IF($B97=725,SUM($G97-(SUM($H97:$I97))),"")</f>
-        <v/>
-      </c>
-      <c r="AL97" t="str">
-        <f>IF($B97=735,SUM($G97-(SUM($H97:$I97))),"")</f>
-        <v/>
-      </c>
-      <c r="AM97" t="str">
-        <f>IF($B97=727,SUM($G97-(SUM($H97:$I97))),"")</f>
-        <v/>
-      </c>
       <c r="AN97" t="str">
         <f>IF($B97=718,SUM($G97-(SUM($H97:$I97))),"")</f>
         <v/>
@@ -17469,7 +16377,7 @@
         <v/>
       </c>
       <c r="AV97" t="str">
-        <f>IF($B97=730,SUM($G97-(SUM($H97:$I97))),"")</f>
+        <f>IF($B97=735,SUM($G97-(SUM($H97:$I97))),"")</f>
         <v/>
       </c>
     </row>
@@ -17607,18 +16515,6 @@
         <f>IF($B98=737,SUM($G98-(SUM($H98:$I98))),"")</f>
         <v/>
       </c>
-      <c r="AK98" t="str">
-        <f>IF($B98=725,SUM($G98-(SUM($H98:$I98))),"")</f>
-        <v/>
-      </c>
-      <c r="AL98" t="str">
-        <f>IF($B98=735,SUM($G98-(SUM($H98:$I98))),"")</f>
-        <v/>
-      </c>
-      <c r="AM98" t="str">
-        <f>IF($B98=727,SUM($G98-(SUM($H98:$I98))),"")</f>
-        <v/>
-      </c>
       <c r="AN98" t="str">
         <f>IF($B98=718,SUM($G98-(SUM($H98:$I98))),"")</f>
         <v/>
@@ -17652,7 +16548,7 @@
         <v/>
       </c>
       <c r="AV98" t="str">
-        <f>IF($B98=730,SUM($G98-(SUM($H98:$I98))),"")</f>
+        <f>IF($B98=735,SUM($G98-(SUM($H98:$I98))),"")</f>
         <v/>
       </c>
     </row>
@@ -17789,18 +16685,6 @@
         <f>IF($B99=737,SUM($G99-(SUM($H99:$I99))),"")</f>
         <v/>
       </c>
-      <c r="AK99" t="str">
-        <f>IF($B99=725,SUM($G99-(SUM($H99:$I99))),"")</f>
-        <v/>
-      </c>
-      <c r="AL99" t="str">
-        <f>IF($B99=735,SUM($G99-(SUM($H99:$I99))),"")</f>
-        <v/>
-      </c>
-      <c r="AM99" t="str">
-        <f>IF($B99=727,SUM($G99-(SUM($H99:$I99))),"")</f>
-        <v/>
-      </c>
       <c r="AN99" t="str">
         <f>IF($B99=718,SUM($G99-(SUM($H99:$I99))),"")</f>
         <v/>
@@ -17834,7 +16718,7 @@
         <v/>
       </c>
       <c r="AV99" t="str">
-        <f>IF($B99=730,SUM($G99-(SUM($H99:$I99))),"")</f>
+        <f>IF($B99=735,SUM($G99-(SUM($H99:$I99))),"")</f>
         <v/>
       </c>
     </row>
@@ -17972,18 +16856,6 @@
         <f>IF($B100=737,SUM($G100-(SUM($H100:$I100))),"")</f>
         <v/>
       </c>
-      <c r="AK100" t="str">
-        <f>IF($B100=725,SUM($G100-(SUM($H100:$I100))),"")</f>
-        <v/>
-      </c>
-      <c r="AL100" t="str">
-        <f>IF($B100=735,SUM($G100-(SUM($H100:$I100))),"")</f>
-        <v/>
-      </c>
-      <c r="AM100" t="str">
-        <f>IF($B100=727,SUM($G100-(SUM($H100:$I100))),"")</f>
-        <v/>
-      </c>
       <c r="AN100" t="str">
         <f>IF($B100=718,SUM($G100-(SUM($H100:$I100))),"")</f>
         <v/>
@@ -18017,7 +16889,7 @@
         <v/>
       </c>
       <c r="AV100" t="str">
-        <f>IF($B100=730,SUM($G100-(SUM($H100:$I100))),"")</f>
+        <f>IF($B100=735,SUM($G100-(SUM($H100:$I100))),"")</f>
         <v/>
       </c>
     </row>
@@ -18149,18 +17021,6 @@
         <f>IF($B101=737,SUM($G101-(SUM($H101:$I101))),"")</f>
         <v/>
       </c>
-      <c r="AK101" t="str">
-        <f>IF($B101=725,SUM($G101-(SUM($H101:$I101))),"")</f>
-        <v/>
-      </c>
-      <c r="AL101" t="str">
-        <f>IF($B101=735,SUM($G101-(SUM($H101:$I101))),"")</f>
-        <v/>
-      </c>
-      <c r="AM101" t="str">
-        <f>IF($B101=727,SUM($G101-(SUM($H101:$I101))),"")</f>
-        <v/>
-      </c>
       <c r="AN101" t="str">
         <f>IF($B101=718,SUM($G101-(SUM($H101:$I101))),"")</f>
         <v/>
@@ -18194,7 +17054,7 @@
         <v/>
       </c>
       <c r="AV101" t="str">
-        <f>IF($B101=730,SUM($G101-(SUM($H101:$I101))),"")</f>
+        <f>IF($B101=735,SUM($G101-(SUM($H101:$I101))),"")</f>
         <v/>
       </c>
     </row>
@@ -18326,18 +17186,6 @@
         <f>IF($B102=737,SUM($G102-(SUM($H102:$I102))),"")</f>
         <v/>
       </c>
-      <c r="AK102" t="str">
-        <f>IF($B102=725,SUM($G102-(SUM($H102:$I102))),"")</f>
-        <v/>
-      </c>
-      <c r="AL102" t="str">
-        <f>IF($B102=735,SUM($G102-(SUM($H102:$I102))),"")</f>
-        <v/>
-      </c>
-      <c r="AM102" t="str">
-        <f>IF($B102=727,SUM($G102-(SUM($H102:$I102))),"")</f>
-        <v/>
-      </c>
       <c r="AN102" t="str">
         <f>IF($B102=718,SUM($G102-(SUM($H102:$I102))),"")</f>
         <v/>
@@ -18371,7 +17219,7 @@
         <v/>
       </c>
       <c r="AV102" t="str">
-        <f>IF($B102=730,SUM($G102-(SUM($H102:$I102))),"")</f>
+        <f>IF($B102=735,SUM($G102-(SUM($H102:$I102))),"")</f>
         <v/>
       </c>
     </row>
@@ -18503,18 +17351,6 @@
         <f>IF($B103=737,SUM($G103-(SUM($H103:$I103))),"")</f>
         <v/>
       </c>
-      <c r="AK103" t="str">
-        <f>IF($B103=725,SUM($G103-(SUM($H103:$I103))),"")</f>
-        <v/>
-      </c>
-      <c r="AL103" t="str">
-        <f>IF($B103=735,SUM($G103-(SUM($H103:$I103))),"")</f>
-        <v/>
-      </c>
-      <c r="AM103" t="str">
-        <f>IF($B103=727,SUM($G103-(SUM($H103:$I103))),"")</f>
-        <v/>
-      </c>
       <c r="AN103" t="str">
         <f>IF($B103=718,SUM($G103-(SUM($H103:$I103))),"")</f>
         <v/>
@@ -18548,7 +17384,7 @@
         <v/>
       </c>
       <c r="AV103" t="str">
-        <f>IF($B103=730,SUM($G103-(SUM($H103:$I103))),"")</f>
+        <f>IF($B103=735,SUM($G103-(SUM($H103:$I103))),"")</f>
         <v/>
       </c>
     </row>
@@ -18680,18 +17516,6 @@
         <f>IF($B104=737,SUM($G104-(SUM($H104:$I104))),"")</f>
         <v/>
       </c>
-      <c r="AK104" t="str">
-        <f>IF($B104=725,SUM($G104-(SUM($H104:$I104))),"")</f>
-        <v/>
-      </c>
-      <c r="AL104" t="str">
-        <f>IF($B104=735,SUM($G104-(SUM($H104:$I104))),"")</f>
-        <v/>
-      </c>
-      <c r="AM104" t="str">
-        <f>IF($B104=727,SUM($G104-(SUM($H104:$I104))),"")</f>
-        <v/>
-      </c>
       <c r="AN104" t="str">
         <f>IF($B104=718,SUM($G104-(SUM($H104:$I104))),"")</f>
         <v/>
@@ -18725,7 +17549,7 @@
         <v/>
       </c>
       <c r="AV104" t="str">
-        <f>IF($B104=730,SUM($G104-(SUM($H104:$I104))),"")</f>
+        <f>IF($B104=735,SUM($G104-(SUM($H104:$I104))),"")</f>
         <v/>
       </c>
     </row>
